--- a/Versão5/SIS/Ontologia_Tubulacao.xlsx
+++ b/Versão5/SIS/Ontologia_Tubulacao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF2E99F-B51D-4CCA-A6BA-D2BB59D790F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABF7F2F-79F6-4C4B-B272-8097D32F6FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4924" uniqueCount="871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4942" uniqueCount="875">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2678,13 +2678,25 @@
     <t>Parâmetro Rvt</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>ClasseI IFC</t>
   </si>
   <si>
     <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
   </si>
 </sst>
 </file>
@@ -2794,7 +2806,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2933,6 +2945,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -3035,7 +3053,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3263,11 +3281,132 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3376,46 +3515,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3453,14 +3552,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3532,9 +3623,9 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFFBE79D"/>
       <color rgb="FFE49EDD"/>
       <color rgb="FFFDF2CB"/>
-      <color rgb="FFFBE79D"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3896,15 +3987,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="66.53515625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="26"/>
+    <col min="1" max="1" width="9.28515625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="66.5703125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -3915,7 +4006,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -3926,7 +4017,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -3937,7 +4028,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -3948,7 +4039,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -3960,7 +4051,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -3972,7 +4063,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3983,7 +4074,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
         <v>54</v>
       </c>
@@ -3994,7 +4085,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -4005,7 +4096,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -4016,7 +4107,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -4027,7 +4118,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -4038,7 +4129,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -4049,7 +4140,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -4060,7 +4151,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -4071,7 +4162,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -4082,7 +4173,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -4093,19 +4184,19 @@
         <v>488</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="28">
         <f ca="1">NOW()</f>
-        <v>46253.805000347224</v>
+        <v>46260.358396875003</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -4116,7 +4207,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -4127,7 +4218,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -4138,7 +4229,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -4149,7 +4240,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -4160,7 +4251,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="56" customFormat="1" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="56" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>486</v>
       </c>
@@ -4180,38 +4271,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D59519-D9E5-4433-9132-270924474650}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC128"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC129"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.23046875" style="67" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.07421875" style="67" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="5.765625" style="67" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" style="67" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.3046875" style="67" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.23046875" style="67" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.23046875" style="67" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="74.4609375" style="67" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="72" style="67" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="57.921875" style="67" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.61328125" style="67" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.69140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.23046875" style="67" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.23046875" style="67" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.69140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.69140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.15234375" style="67" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.765625" style="67" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26.07421875" style="67" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.5703125" style="67" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="101.140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="97" style="67" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="79.140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10" style="67" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" style="67" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="36" style="67" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="67" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9" style="67" bestFit="1" customWidth="1"/>
-    <col min="30" max="33" width="5.3046875" style="67" customWidth="1"/>
-    <col min="34" max="16384" width="9.15234375" style="67"/>
+    <col min="29" max="29" width="12.42578125" style="67" bestFit="1" customWidth="1"/>
+    <col min="30" max="33" width="5.28515625" style="67" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="67"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="76" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" s="76" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="73">
         <v>1</v>
       </c>
@@ -4291,16 +4383,16 @@
         <v>867</v>
       </c>
       <c r="AA1" s="53" t="s">
+        <v>868</v>
+      </c>
+      <c r="AB1" s="53" t="s">
         <v>869</v>
-      </c>
-      <c r="AB1" s="53" t="s">
-        <v>870</v>
       </c>
       <c r="AC1" s="53" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="69">
         <v>2</v>
       </c>
@@ -4384,20 +4476,20 @@
       <c r="Y2" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z2" s="21" t="s">
-        <v>868</v>
+      <c r="Z2" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA2" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB2" s="21" t="s">
-        <v>868</v>
+      <c r="AB2" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="21" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="69">
         <v>3</v>
       </c>
@@ -4481,20 +4573,20 @@
       <c r="Y3" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z3" s="21" t="s">
-        <v>868</v>
+      <c r="Z3" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA3" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB3" s="21" t="s">
-        <v>868</v>
+      <c r="AB3" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="21" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="69">
         <v>4</v>
       </c>
@@ -4578,20 +4670,20 @@
       <c r="Y4" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z4" s="21" t="s">
-        <v>868</v>
+      <c r="Z4" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA4" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB4" s="21" t="s">
-        <v>868</v>
+      <c r="AB4" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="21" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="69">
         <v>5</v>
       </c>
@@ -4675,20 +4767,20 @@
       <c r="Y5" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z5" s="21" t="s">
-        <v>868</v>
+      <c r="Z5" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB5" s="21" t="s">
-        <v>868</v>
+      <c r="AB5" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="21" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="69">
         <v>6</v>
       </c>
@@ -4772,20 +4864,20 @@
       <c r="Y6" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z6" s="21" t="s">
-        <v>868</v>
+      <c r="Z6" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB6" s="21" t="s">
-        <v>868</v>
+      <c r="AB6" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="21" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="69">
         <v>7</v>
       </c>
@@ -4869,20 +4961,20 @@
       <c r="Y7" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z7" s="21" t="s">
-        <v>868</v>
+      <c r="Z7" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA7" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB7" s="21" t="s">
-        <v>868</v>
+      <c r="AB7" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="21" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="69">
         <v>8</v>
       </c>
@@ -4966,20 +5058,20 @@
       <c r="Y8" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z8" s="21" t="s">
-        <v>868</v>
+      <c r="Z8" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB8" s="21" t="s">
-        <v>868</v>
+      <c r="AB8" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="21" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="69">
         <v>9</v>
       </c>
@@ -5063,20 +5155,20 @@
       <c r="Y9" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z9" s="21" t="s">
-        <v>868</v>
+      <c r="Z9" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="68" t="s">
         <v>525</v>
       </c>
-      <c r="AB9" s="21" t="s">
-        <v>868</v>
+      <c r="AB9" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="69">
         <v>10</v>
       </c>
@@ -5160,20 +5252,20 @@
       <c r="Y10" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z10" s="21" t="s">
-        <v>868</v>
+      <c r="Z10" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="68" t="s">
         <v>527</v>
       </c>
-      <c r="AB10" s="21" t="s">
-        <v>868</v>
+      <c r="AB10" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69">
         <v>11</v>
       </c>
@@ -5257,20 +5349,20 @@
       <c r="Y11" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z11" s="21" t="s">
-        <v>868</v>
+      <c r="Z11" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="68" t="s">
         <v>528</v>
       </c>
-      <c r="AB11" s="21" t="s">
-        <v>868</v>
+      <c r="AB11" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="69">
         <v>12</v>
       </c>
@@ -5354,20 +5446,20 @@
       <c r="Y12" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z12" s="21" t="s">
-        <v>868</v>
+      <c r="Z12" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="68" t="s">
         <v>529</v>
       </c>
-      <c r="AB12" s="21" t="s">
-        <v>868</v>
+      <c r="AB12" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="69">
         <v>13</v>
       </c>
@@ -5451,20 +5543,20 @@
       <c r="Y13" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z13" s="21" t="s">
-        <v>868</v>
+      <c r="Z13" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="68" t="s">
         <v>530</v>
       </c>
-      <c r="AB13" s="21" t="s">
-        <v>868</v>
+      <c r="AB13" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="69">
         <v>14</v>
       </c>
@@ -5548,20 +5640,20 @@
       <c r="Y14" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z14" s="21" t="s">
-        <v>868</v>
+      <c r="Z14" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="68" t="s">
         <v>531</v>
       </c>
-      <c r="AB14" s="21" t="s">
-        <v>868</v>
+      <c r="AB14" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="69">
         <v>15</v>
       </c>
@@ -5645,20 +5737,20 @@
       <c r="Y15" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z15" s="21" t="s">
-        <v>868</v>
+      <c r="Z15" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA15" s="68" t="s">
         <v>532</v>
       </c>
-      <c r="AB15" s="21" t="s">
-        <v>868</v>
+      <c r="AB15" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC15" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="69">
         <v>16</v>
       </c>
@@ -5742,20 +5834,20 @@
       <c r="Y16" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z16" s="21" t="s">
-        <v>868</v>
+      <c r="Z16" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA16" s="68" t="s">
         <v>533</v>
       </c>
-      <c r="AB16" s="21" t="s">
-        <v>868</v>
+      <c r="AB16" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC16" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="69">
         <v>17</v>
       </c>
@@ -5839,20 +5931,20 @@
       <c r="Y17" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z17" s="21" t="s">
-        <v>868</v>
+      <c r="Z17" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA17" s="68" t="s">
         <v>534</v>
       </c>
-      <c r="AB17" s="21" t="s">
-        <v>868</v>
+      <c r="AB17" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC17" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="69">
         <v>18</v>
       </c>
@@ -5936,20 +6028,20 @@
       <c r="Y18" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z18" s="21" t="s">
-        <v>868</v>
+      <c r="Z18" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA18" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB18" s="21" t="s">
-        <v>868</v>
+      <c r="AB18" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC18" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="69">
         <v>19</v>
       </c>
@@ -6033,20 +6125,20 @@
       <c r="Y19" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z19" s="21" t="s">
-        <v>868</v>
+      <c r="Z19" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA19" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB19" s="21" t="s">
-        <v>868</v>
+      <c r="AB19" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC19" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="69">
         <v>20</v>
       </c>
@@ -6130,20 +6222,20 @@
       <c r="Y20" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z20" s="21" t="s">
-        <v>868</v>
+      <c r="Z20" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA20" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB20" s="21" t="s">
-        <v>868</v>
+      <c r="AB20" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC20" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="69">
         <v>21</v>
       </c>
@@ -6227,20 +6319,20 @@
       <c r="Y21" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z21" s="21" t="s">
-        <v>868</v>
+      <c r="Z21" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA21" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB21" s="21" t="s">
-        <v>868</v>
+      <c r="AB21" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC21" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="69">
         <v>22</v>
       </c>
@@ -6324,20 +6416,20 @@
       <c r="Y22" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z22" s="21" t="s">
-        <v>868</v>
+      <c r="Z22" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA22" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB22" s="21" t="s">
-        <v>868</v>
+      <c r="AB22" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC22" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="69">
         <v>23</v>
       </c>
@@ -6421,20 +6513,20 @@
       <c r="Y23" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z23" s="21" t="s">
-        <v>868</v>
+      <c r="Z23" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA23" s="68" t="s">
         <v>538</v>
       </c>
-      <c r="AB23" s="21" t="s">
-        <v>868</v>
+      <c r="AB23" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC23" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="69">
         <v>24</v>
       </c>
@@ -6518,20 +6610,20 @@
       <c r="Y24" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z24" s="21" t="s">
-        <v>868</v>
+      <c r="Z24" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA24" s="68" t="s">
         <v>539</v>
       </c>
-      <c r="AB24" s="21" t="s">
-        <v>868</v>
+      <c r="AB24" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC24" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="69">
         <v>25</v>
       </c>
@@ -6615,20 +6707,20 @@
       <c r="Y25" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z25" s="21" t="s">
-        <v>868</v>
+      <c r="Z25" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA25" s="68" t="s">
         <v>540</v>
       </c>
-      <c r="AB25" s="21" t="s">
-        <v>868</v>
+      <c r="AB25" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC25" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="69">
         <v>26</v>
       </c>
@@ -6712,20 +6804,20 @@
       <c r="Y26" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z26" s="21" t="s">
-        <v>868</v>
+      <c r="Z26" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA26" s="68" t="s">
         <v>540</v>
       </c>
-      <c r="AB26" s="21" t="s">
-        <v>868</v>
+      <c r="AB26" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC26" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="69">
         <v>27</v>
       </c>
@@ -6809,20 +6901,20 @@
       <c r="Y27" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z27" s="21" t="s">
-        <v>868</v>
+      <c r="Z27" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA27" s="68" t="s">
         <v>541</v>
       </c>
-      <c r="AB27" s="21" t="s">
-        <v>868</v>
+      <c r="AB27" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC27" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="69">
         <v>28</v>
       </c>
@@ -6906,20 +6998,20 @@
       <c r="Y28" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z28" s="21" t="s">
-        <v>868</v>
+      <c r="Z28" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA28" s="68" t="s">
         <v>542</v>
       </c>
-      <c r="AB28" s="21" t="s">
-        <v>868</v>
+      <c r="AB28" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC28" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="69">
         <v>29</v>
       </c>
@@ -7003,20 +7095,20 @@
       <c r="Y29" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z29" s="21" t="s">
-        <v>868</v>
+      <c r="Z29" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA29" s="68" t="s">
         <v>543</v>
       </c>
-      <c r="AB29" s="21" t="s">
-        <v>868</v>
+      <c r="AB29" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC29" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="69">
         <v>30</v>
       </c>
@@ -7100,20 +7192,20 @@
       <c r="Y30" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z30" s="21" t="s">
-        <v>868</v>
+      <c r="Z30" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA30" s="68" t="s">
         <v>540</v>
       </c>
-      <c r="AB30" s="21" t="s">
-        <v>868</v>
+      <c r="AB30" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC30" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="69">
         <v>31</v>
       </c>
@@ -7197,20 +7289,20 @@
       <c r="Y31" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z31" s="21" t="s">
-        <v>868</v>
+      <c r="Z31" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA31" s="68" t="s">
         <v>541</v>
       </c>
-      <c r="AB31" s="21" t="s">
-        <v>868</v>
+      <c r="AB31" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC31" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="69">
         <v>32</v>
       </c>
@@ -7294,20 +7386,20 @@
       <c r="Y32" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z32" s="21" t="s">
-        <v>868</v>
+      <c r="Z32" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA32" s="68" t="s">
         <v>542</v>
       </c>
-      <c r="AB32" s="21" t="s">
-        <v>868</v>
+      <c r="AB32" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC32" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="69">
         <v>33</v>
       </c>
@@ -7391,20 +7483,20 @@
       <c r="Y33" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z33" s="21" t="s">
-        <v>868</v>
+      <c r="Z33" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA33" s="68" t="s">
         <v>543</v>
       </c>
-      <c r="AB33" s="21" t="s">
-        <v>868</v>
+      <c r="AB33" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC33" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="69">
         <v>34</v>
       </c>
@@ -7488,20 +7580,20 @@
       <c r="Y34" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z34" s="21" t="s">
-        <v>868</v>
+      <c r="Z34" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA34" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="AB34" s="21" t="s">
-        <v>868</v>
+      <c r="AB34" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC34" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="69">
         <v>35</v>
       </c>
@@ -7585,20 +7677,20 @@
       <c r="Y35" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z35" s="21" t="s">
-        <v>868</v>
+      <c r="Z35" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA35" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="AB35" s="21" t="s">
-        <v>868</v>
+      <c r="AB35" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC35" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="69">
         <v>36</v>
       </c>
@@ -7682,20 +7774,20 @@
       <c r="Y36" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z36" s="21" t="s">
-        <v>868</v>
+      <c r="Z36" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA36" s="68" t="s">
         <v>545</v>
       </c>
-      <c r="AB36" s="21" t="s">
-        <v>868</v>
+      <c r="AB36" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC36" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="69">
         <v>37</v>
       </c>
@@ -7779,20 +7871,20 @@
       <c r="Y37" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z37" s="21" t="s">
-        <v>868</v>
+      <c r="Z37" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA37" s="68" t="s">
         <v>546</v>
       </c>
-      <c r="AB37" s="21" t="s">
-        <v>868</v>
+      <c r="AB37" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC37" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="69">
         <v>38</v>
       </c>
@@ -7876,20 +7968,20 @@
       <c r="Y38" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z38" s="21" t="s">
-        <v>868</v>
+      <c r="Z38" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA38" s="68" t="s">
         <v>547</v>
       </c>
-      <c r="AB38" s="21" t="s">
-        <v>868</v>
+      <c r="AB38" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC38" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="69">
         <v>39</v>
       </c>
@@ -7973,20 +8065,20 @@
       <c r="Y39" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z39" s="21" t="s">
-        <v>868</v>
+      <c r="Z39" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA39" s="68" t="s">
         <v>541</v>
       </c>
-      <c r="AB39" s="21" t="s">
-        <v>868</v>
+      <c r="AB39" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC39" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="69">
         <v>40</v>
       </c>
@@ -8070,20 +8162,20 @@
       <c r="Y40" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z40" s="21" t="s">
-        <v>868</v>
+      <c r="Z40" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA40" s="68" t="s">
         <v>533</v>
       </c>
-      <c r="AB40" s="21" t="s">
-        <v>868</v>
+      <c r="AB40" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC40" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="69">
         <v>41</v>
       </c>
@@ -8167,20 +8259,20 @@
       <c r="Y41" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z41" s="21" t="s">
-        <v>868</v>
+      <c r="Z41" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA41" s="68" t="s">
         <v>533</v>
       </c>
-      <c r="AB41" s="21" t="s">
-        <v>868</v>
+      <c r="AB41" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC41" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="69">
         <v>42</v>
       </c>
@@ -8264,20 +8356,20 @@
       <c r="Y42" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z42" s="21" t="s">
-        <v>868</v>
+      <c r="Z42" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA42" s="68" t="s">
         <v>548</v>
       </c>
-      <c r="AB42" s="21" t="s">
-        <v>868</v>
+      <c r="AB42" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC42" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="69">
         <v>43</v>
       </c>
@@ -8361,20 +8453,20 @@
       <c r="Y43" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z43" s="21" t="s">
-        <v>868</v>
+      <c r="Z43" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA43" s="68" t="s">
         <v>549</v>
       </c>
-      <c r="AB43" s="21" t="s">
-        <v>868</v>
+      <c r="AB43" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC43" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="69">
         <v>44</v>
       </c>
@@ -8458,20 +8550,20 @@
       <c r="Y44" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z44" s="21" t="s">
-        <v>868</v>
+      <c r="Z44" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA44" s="68" t="s">
         <v>550</v>
       </c>
-      <c r="AB44" s="21" t="s">
-        <v>868</v>
+      <c r="AB44" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC44" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="69">
         <v>45</v>
       </c>
@@ -8555,20 +8647,20 @@
       <c r="Y45" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z45" s="21" t="s">
-        <v>868</v>
+      <c r="Z45" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA45" s="68" t="s">
         <v>551</v>
       </c>
-      <c r="AB45" s="21" t="s">
-        <v>868</v>
+      <c r="AB45" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC45" s="21" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="69">
         <v>46</v>
       </c>
@@ -8652,20 +8744,20 @@
       <c r="Y46" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z46" s="21" t="s">
-        <v>868</v>
+      <c r="Z46" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA46" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB46" s="21" t="s">
-        <v>868</v>
+      <c r="AB46" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC46" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="69">
         <v>47</v>
       </c>
@@ -8749,20 +8841,20 @@
       <c r="Y47" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z47" s="21" t="s">
-        <v>868</v>
+      <c r="Z47" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA47" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB47" s="21" t="s">
-        <v>868</v>
+      <c r="AB47" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC47" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="69">
         <v>48</v>
       </c>
@@ -8846,20 +8938,20 @@
       <c r="Y48" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z48" s="21" t="s">
-        <v>868</v>
+      <c r="Z48" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA48" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB48" s="21" t="s">
-        <v>868</v>
+      <c r="AB48" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC48" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="69">
         <v>49</v>
       </c>
@@ -8943,20 +9035,20 @@
       <c r="Y49" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z49" s="21" t="s">
-        <v>868</v>
+      <c r="Z49" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA49" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB49" s="21" t="s">
-        <v>868</v>
+      <c r="AB49" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC49" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="69">
         <v>50</v>
       </c>
@@ -9040,20 +9132,20 @@
       <c r="Y50" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z50" s="21" t="s">
-        <v>868</v>
+      <c r="Z50" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA50" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB50" s="21" t="s">
-        <v>868</v>
+      <c r="AB50" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC50" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="69">
         <v>51</v>
       </c>
@@ -9137,20 +9229,20 @@
       <c r="Y51" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z51" s="21" t="s">
-        <v>868</v>
+      <c r="Z51" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA51" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB51" s="21" t="s">
-        <v>868</v>
+      <c r="AB51" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC51" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="69">
         <v>52</v>
       </c>
@@ -9234,20 +9326,20 @@
       <c r="Y52" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z52" s="21" t="s">
-        <v>868</v>
+      <c r="Z52" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA52" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB52" s="21" t="s">
-        <v>868</v>
+      <c r="AB52" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC52" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="69">
         <v>53</v>
       </c>
@@ -9331,20 +9423,20 @@
       <c r="Y53" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z53" s="21" t="s">
-        <v>868</v>
+      <c r="Z53" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA53" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB53" s="21" t="s">
-        <v>868</v>
+      <c r="AB53" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC53" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="69">
         <v>54</v>
       </c>
@@ -9428,20 +9520,20 @@
       <c r="Y54" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z54" s="21" t="s">
-        <v>868</v>
+      <c r="Z54" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA54" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB54" s="21" t="s">
-        <v>868</v>
+      <c r="AB54" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC54" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="69">
         <v>55</v>
       </c>
@@ -9525,20 +9617,20 @@
       <c r="Y55" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z55" s="21" t="s">
-        <v>868</v>
+      <c r="Z55" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA55" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB55" s="21" t="s">
-        <v>868</v>
+      <c r="AB55" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC55" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="69">
         <v>56</v>
       </c>
@@ -9622,20 +9714,20 @@
       <c r="Y56" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z56" s="21" t="s">
-        <v>868</v>
+      <c r="Z56" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA56" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB56" s="21" t="s">
-        <v>868</v>
+      <c r="AB56" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC56" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="69">
         <v>57</v>
       </c>
@@ -9719,20 +9811,20 @@
       <c r="Y57" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z57" s="21" t="s">
-        <v>868</v>
+      <c r="Z57" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA57" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB57" s="21" t="s">
-        <v>868</v>
+      <c r="AB57" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC57" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="69">
         <v>58</v>
       </c>
@@ -9816,20 +9908,20 @@
       <c r="Y58" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z58" s="21" t="s">
-        <v>868</v>
+      <c r="Z58" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA58" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB58" s="21" t="s">
-        <v>868</v>
+      <c r="AB58" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC58" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="69">
         <v>59</v>
       </c>
@@ -9913,20 +10005,20 @@
       <c r="Y59" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z59" s="21" t="s">
-        <v>868</v>
+      <c r="Z59" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA59" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB59" s="21" t="s">
-        <v>868</v>
+      <c r="AB59" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC59" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="69">
         <v>60</v>
       </c>
@@ -10010,20 +10102,20 @@
       <c r="Y60" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z60" s="21" t="s">
-        <v>868</v>
+      <c r="Z60" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA60" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB60" s="21" t="s">
-        <v>868</v>
+      <c r="AB60" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC60" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="69">
         <v>61</v>
       </c>
@@ -10107,20 +10199,20 @@
       <c r="Y61" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z61" s="21" t="s">
-        <v>868</v>
+      <c r="Z61" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA61" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB61" s="21" t="s">
-        <v>868</v>
+      <c r="AB61" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC61" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="69">
         <v>62</v>
       </c>
@@ -10204,20 +10296,20 @@
       <c r="Y62" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z62" s="21" t="s">
-        <v>868</v>
+      <c r="Z62" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA62" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB62" s="21" t="s">
-        <v>868</v>
+      <c r="AB62" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC62" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="69">
         <v>63</v>
       </c>
@@ -10301,20 +10393,20 @@
       <c r="Y63" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z63" s="21" t="s">
-        <v>868</v>
+      <c r="Z63" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA63" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB63" s="21" t="s">
-        <v>868</v>
+      <c r="AB63" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC63" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="69">
         <v>64</v>
       </c>
@@ -10398,20 +10490,20 @@
       <c r="Y64" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z64" s="21" t="s">
-        <v>868</v>
+      <c r="Z64" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA64" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB64" s="21" t="s">
-        <v>868</v>
+      <c r="AB64" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC64" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="69">
         <v>65</v>
       </c>
@@ -10495,20 +10587,20 @@
       <c r="Y65" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z65" s="21" t="s">
-        <v>868</v>
+      <c r="Z65" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA65" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB65" s="21" t="s">
-        <v>868</v>
+      <c r="AB65" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC65" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="69">
         <v>66</v>
       </c>
@@ -10592,20 +10684,20 @@
       <c r="Y66" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z66" s="21" t="s">
-        <v>868</v>
+      <c r="Z66" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA66" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB66" s="21" t="s">
-        <v>868</v>
+      <c r="AB66" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC66" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="69">
         <v>67</v>
       </c>
@@ -10689,20 +10781,20 @@
       <c r="Y67" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z67" s="21" t="s">
-        <v>868</v>
+      <c r="Z67" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA67" s="21" t="s">
         <v>557</v>
       </c>
-      <c r="AB67" s="21" t="s">
-        <v>868</v>
+      <c r="AB67" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC67" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="69">
         <v>68</v>
       </c>
@@ -10786,20 +10878,20 @@
       <c r="Y68" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z68" s="21" t="s">
-        <v>868</v>
+      <c r="Z68" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA68" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB68" s="21" t="s">
-        <v>868</v>
+      <c r="AB68" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC68" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="69">
         <v>69</v>
       </c>
@@ -10883,20 +10975,20 @@
       <c r="Y69" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z69" s="21" t="s">
-        <v>868</v>
+      <c r="Z69" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA69" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB69" s="21" t="s">
-        <v>868</v>
+      <c r="AB69" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC69" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="69">
         <v>70</v>
       </c>
@@ -10980,20 +11072,20 @@
       <c r="Y70" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z70" s="21" t="s">
-        <v>868</v>
+      <c r="Z70" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA70" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB70" s="21" t="s">
-        <v>868</v>
+      <c r="AB70" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC70" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="69">
         <v>71</v>
       </c>
@@ -11077,20 +11169,20 @@
       <c r="Y71" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z71" s="21" t="s">
-        <v>868</v>
+      <c r="Z71" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA71" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB71" s="21" t="s">
-        <v>868</v>
+      <c r="AB71" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC71" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="69">
         <v>72</v>
       </c>
@@ -11174,20 +11266,20 @@
       <c r="Y72" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z72" s="21" t="s">
-        <v>868</v>
+      <c r="Z72" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA72" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB72" s="21" t="s">
-        <v>868</v>
+      <c r="AB72" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC72" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="69">
         <v>73</v>
       </c>
@@ -11271,20 +11363,20 @@
       <c r="Y73" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z73" s="21" t="s">
-        <v>868</v>
+      <c r="Z73" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA73" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB73" s="21" t="s">
-        <v>868</v>
+      <c r="AB73" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC73" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="69">
         <v>74</v>
       </c>
@@ -11368,20 +11460,20 @@
       <c r="Y74" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z74" s="21" t="s">
-        <v>868</v>
+      <c r="Z74" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA74" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB74" s="21" t="s">
-        <v>868</v>
+      <c r="AB74" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC74" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="69">
         <v>75</v>
       </c>
@@ -11465,20 +11557,20 @@
       <c r="Y75" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z75" s="21" t="s">
-        <v>868</v>
+      <c r="Z75" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA75" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB75" s="21" t="s">
-        <v>868</v>
+      <c r="AB75" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC75" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="69">
         <v>76</v>
       </c>
@@ -11562,20 +11654,20 @@
       <c r="Y76" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z76" s="21" t="s">
-        <v>868</v>
+      <c r="Z76" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA76" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB76" s="21" t="s">
-        <v>868</v>
+      <c r="AB76" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC76" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="69">
         <v>77</v>
       </c>
@@ -11659,20 +11751,20 @@
       <c r="Y77" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z77" s="21" t="s">
-        <v>868</v>
+      <c r="Z77" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA77" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB77" s="21" t="s">
-        <v>868</v>
+      <c r="AB77" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC77" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="69">
         <v>78</v>
       </c>
@@ -11756,20 +11848,20 @@
       <c r="Y78" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z78" s="21" t="s">
-        <v>868</v>
+      <c r="Z78" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA78" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB78" s="21" t="s">
-        <v>868</v>
+      <c r="AB78" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC78" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="69">
         <v>79</v>
       </c>
@@ -11853,20 +11945,20 @@
       <c r="Y79" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z79" s="21" t="s">
-        <v>868</v>
+      <c r="Z79" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA79" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB79" s="21" t="s">
-        <v>868</v>
+      <c r="AB79" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC79" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="69">
         <v>80</v>
       </c>
@@ -11950,20 +12042,20 @@
       <c r="Y80" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z80" s="21" t="s">
-        <v>868</v>
+      <c r="Z80" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA80" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB80" s="21" t="s">
-        <v>868</v>
+      <c r="AB80" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC80" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="69">
         <v>81</v>
       </c>
@@ -12047,20 +12139,20 @@
       <c r="Y81" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z81" s="21" t="s">
-        <v>868</v>
+      <c r="Z81" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA81" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB81" s="21" t="s">
-        <v>868</v>
+      <c r="AB81" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC81" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="69">
         <v>82</v>
       </c>
@@ -12144,20 +12236,20 @@
       <c r="Y82" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z82" s="21" t="s">
-        <v>868</v>
+      <c r="Z82" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA82" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB82" s="21" t="s">
-        <v>868</v>
+      <c r="AB82" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC82" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="69">
         <v>83</v>
       </c>
@@ -12241,20 +12333,20 @@
       <c r="Y83" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z83" s="21" t="s">
-        <v>868</v>
+      <c r="Z83" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA83" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB83" s="21" t="s">
-        <v>868</v>
+      <c r="AB83" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC83" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="69">
         <v>84</v>
       </c>
@@ -12338,20 +12430,20 @@
       <c r="Y84" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z84" s="21" t="s">
-        <v>868</v>
+      <c r="Z84" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA84" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="AB84" s="21" t="s">
-        <v>868</v>
+      <c r="AB84" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC84" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="69">
         <v>85</v>
       </c>
@@ -12435,20 +12527,20 @@
       <c r="Y85" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z85" s="21" t="s">
-        <v>868</v>
+      <c r="Z85" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA85" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="AB85" s="21" t="s">
-        <v>868</v>
+      <c r="AB85" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC85" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="69">
         <v>86</v>
       </c>
@@ -12532,20 +12624,20 @@
       <c r="Y86" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z86" s="21" t="s">
-        <v>868</v>
+      <c r="Z86" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA86" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="AB86" s="21" t="s">
-        <v>868</v>
+      <c r="AB86" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC86" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="69">
         <v>87</v>
       </c>
@@ -12629,20 +12721,20 @@
       <c r="Y87" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z87" s="21" t="s">
-        <v>868</v>
+      <c r="Z87" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA87" s="21" t="s">
         <v>561</v>
       </c>
-      <c r="AB87" s="21" t="s">
-        <v>868</v>
+      <c r="AB87" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC87" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="69">
         <v>88</v>
       </c>
@@ -12726,20 +12818,20 @@
       <c r="Y88" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z88" s="21" t="s">
-        <v>868</v>
+      <c r="Z88" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA88" s="21" t="s">
         <v>561</v>
       </c>
-      <c r="AB88" s="21" t="s">
-        <v>868</v>
+      <c r="AB88" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC88" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="69">
         <v>89</v>
       </c>
@@ -12823,20 +12915,20 @@
       <c r="Y89" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z89" s="21" t="s">
-        <v>868</v>
+      <c r="Z89" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA89" s="21" t="s">
         <v>561</v>
       </c>
-      <c r="AB89" s="21" t="s">
-        <v>868</v>
+      <c r="AB89" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC89" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="69">
         <v>90</v>
       </c>
@@ -12920,20 +13012,20 @@
       <c r="Y90" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z90" s="21" t="s">
-        <v>868</v>
+      <c r="Z90" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA90" s="21" t="s">
         <v>562</v>
       </c>
-      <c r="AB90" s="21" t="s">
-        <v>868</v>
+      <c r="AB90" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC90" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="69">
         <v>91</v>
       </c>
@@ -13017,20 +13109,20 @@
       <c r="Y91" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z91" s="21" t="s">
-        <v>868</v>
+      <c r="Z91" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA91" s="68" t="s">
         <v>563</v>
       </c>
-      <c r="AB91" s="21" t="s">
-        <v>868</v>
+      <c r="AB91" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC91" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="69">
         <v>92</v>
       </c>
@@ -13114,20 +13206,20 @@
       <c r="Y92" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z92" s="21" t="s">
-        <v>868</v>
+      <c r="Z92" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA92" s="68" t="s">
         <v>564</v>
       </c>
-      <c r="AB92" s="21" t="s">
-        <v>868</v>
+      <c r="AB92" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC92" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="69">
         <v>93</v>
       </c>
@@ -13211,20 +13303,20 @@
       <c r="Y93" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z93" s="21" t="s">
-        <v>868</v>
+      <c r="Z93" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA93" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB93" s="21" t="s">
-        <v>868</v>
+      <c r="AB93" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC93" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="69">
         <v>94</v>
       </c>
@@ -13308,20 +13400,20 @@
       <c r="Y94" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z94" s="21" t="s">
-        <v>868</v>
+      <c r="Z94" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA94" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB94" s="21" t="s">
-        <v>868</v>
+      <c r="AB94" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC94" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="69">
         <v>95</v>
       </c>
@@ -13405,20 +13497,20 @@
       <c r="Y95" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z95" s="21" t="s">
-        <v>868</v>
+      <c r="Z95" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA95" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB95" s="21" t="s">
-        <v>868</v>
+      <c r="AB95" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC95" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="69">
         <v>96</v>
       </c>
@@ -13502,20 +13594,20 @@
       <c r="Y96" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z96" s="21" t="s">
-        <v>868</v>
+      <c r="Z96" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA96" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB96" s="21" t="s">
-        <v>868</v>
+      <c r="AB96" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC96" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="69">
         <v>97</v>
       </c>
@@ -13599,20 +13691,20 @@
       <c r="Y97" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z97" s="21" t="s">
-        <v>868</v>
+      <c r="Z97" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA97" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB97" s="21" t="s">
-        <v>868</v>
+      <c r="AB97" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC97" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="69">
         <v>98</v>
       </c>
@@ -13696,20 +13788,20 @@
       <c r="Y98" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z98" s="21" t="s">
-        <v>868</v>
+      <c r="Z98" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA98" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB98" s="21" t="s">
-        <v>868</v>
+      <c r="AB98" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC98" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="69">
         <v>99</v>
       </c>
@@ -13793,20 +13885,20 @@
       <c r="Y99" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z99" s="21" t="s">
-        <v>868</v>
+      <c r="Z99" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA99" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB99" s="21" t="s">
-        <v>868</v>
+      <c r="AB99" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC99" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="69">
         <v>100</v>
       </c>
@@ -13890,20 +13982,20 @@
       <c r="Y100" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z100" s="21" t="s">
-        <v>868</v>
+      <c r="Z100" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA100" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB100" s="21" t="s">
-        <v>868</v>
+      <c r="AB100" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC100" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="69">
         <v>101</v>
       </c>
@@ -13987,20 +14079,20 @@
       <c r="Y101" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z101" s="21" t="s">
-        <v>868</v>
+      <c r="Z101" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA101" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB101" s="21" t="s">
-        <v>868</v>
+      <c r="AB101" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC101" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="69">
         <v>102</v>
       </c>
@@ -14084,20 +14176,20 @@
       <c r="Y102" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z102" s="21" t="s">
-        <v>868</v>
+      <c r="Z102" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA102" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB102" s="21" t="s">
-        <v>868</v>
+      <c r="AB102" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC102" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="69">
         <v>103</v>
       </c>
@@ -14181,20 +14273,20 @@
       <c r="Y103" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z103" s="21" t="s">
-        <v>868</v>
+      <c r="Z103" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA103" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB103" s="21" t="s">
-        <v>868</v>
+      <c r="AB103" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC103" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="69">
         <v>104</v>
       </c>
@@ -14278,20 +14370,20 @@
       <c r="Y104" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z104" s="21" t="s">
-        <v>868</v>
+      <c r="Z104" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA104" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB104" s="21" t="s">
-        <v>868</v>
+      <c r="AB104" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC104" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="69">
         <v>105</v>
       </c>
@@ -14375,20 +14467,20 @@
       <c r="Y105" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z105" s="21" t="s">
-        <v>868</v>
+      <c r="Z105" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA105" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB105" s="21" t="s">
-        <v>868</v>
+      <c r="AB105" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC105" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="69">
         <v>106</v>
       </c>
@@ -14472,20 +14564,20 @@
       <c r="Y106" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z106" s="21" t="s">
-        <v>868</v>
+      <c r="Z106" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA106" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB106" s="21" t="s">
-        <v>868</v>
+      <c r="AB106" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC106" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="69">
         <v>107</v>
       </c>
@@ -14569,20 +14661,20 @@
       <c r="Y107" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z107" s="21" t="s">
-        <v>868</v>
+      <c r="Z107" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA107" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB107" s="21" t="s">
-        <v>868</v>
+      <c r="AB107" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC107" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="69">
         <v>108</v>
       </c>
@@ -14666,20 +14758,20 @@
       <c r="Y108" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z108" s="21" t="s">
-        <v>868</v>
+      <c r="Z108" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA108" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB108" s="21" t="s">
-        <v>868</v>
+      <c r="AB108" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC108" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="69">
         <v>109</v>
       </c>
@@ -14763,20 +14855,20 @@
       <c r="Y109" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z109" s="21" t="s">
-        <v>868</v>
+      <c r="Z109" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA109" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB109" s="21" t="s">
-        <v>868</v>
+      <c r="AB109" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC109" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="69">
         <v>110</v>
       </c>
@@ -14860,20 +14952,20 @@
       <c r="Y110" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z110" s="21" t="s">
-        <v>868</v>
+      <c r="Z110" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA110" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB110" s="21" t="s">
-        <v>868</v>
+      <c r="AB110" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC110" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="69">
         <v>111</v>
       </c>
@@ -14957,20 +15049,20 @@
       <c r="Y111" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z111" s="21" t="s">
-        <v>868</v>
+      <c r="Z111" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA111" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB111" s="21" t="s">
-        <v>868</v>
+      <c r="AB111" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC111" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="69">
         <v>112</v>
       </c>
@@ -15054,20 +15146,20 @@
       <c r="Y112" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z112" s="21" t="s">
-        <v>868</v>
+      <c r="Z112" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA112" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB112" s="21" t="s">
-        <v>868</v>
+      <c r="AB112" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC112" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="69">
         <v>113</v>
       </c>
@@ -15151,20 +15243,20 @@
       <c r="Y113" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z113" s="21" t="s">
-        <v>868</v>
+      <c r="Z113" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA113" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB113" s="21" t="s">
-        <v>868</v>
+      <c r="AB113" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC113" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="69">
         <v>114</v>
       </c>
@@ -15248,20 +15340,20 @@
       <c r="Y114" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z114" s="21" t="s">
-        <v>868</v>
+      <c r="Z114" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA114" s="21" t="s">
         <v>567</v>
       </c>
-      <c r="AB114" s="21" t="s">
-        <v>868</v>
+      <c r="AB114" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC114" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="69">
         <v>115</v>
       </c>
@@ -15345,20 +15437,20 @@
       <c r="Y115" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z115" s="21" t="s">
-        <v>868</v>
+      <c r="Z115" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA115" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB115" s="21" t="s">
-        <v>868</v>
+      <c r="AB115" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC115" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="69">
         <v>116</v>
       </c>
@@ -15442,20 +15534,20 @@
       <c r="Y116" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z116" s="21" t="s">
-        <v>868</v>
+      <c r="Z116" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA116" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB116" s="21" t="s">
-        <v>868</v>
+      <c r="AB116" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC116" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="69">
         <v>117</v>
       </c>
@@ -15536,20 +15628,20 @@
       <c r="Y117" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z117" s="21" t="s">
-        <v>868</v>
+      <c r="Z117" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA117" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB117" s="21" t="s">
-        <v>868</v>
+      <c r="AB117" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC117" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="69">
         <v>118</v>
       </c>
@@ -15630,20 +15722,20 @@
       <c r="Y118" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z118" s="21" t="s">
-        <v>868</v>
+      <c r="Z118" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA118" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB118" s="21" t="s">
-        <v>868</v>
+      <c r="AB118" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC118" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="69">
         <v>119</v>
       </c>
@@ -15724,20 +15816,20 @@
       <c r="Y119" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z119" s="21" t="s">
-        <v>868</v>
+      <c r="Z119" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA119" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB119" s="21" t="s">
-        <v>868</v>
+      <c r="AB119" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC119" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="69">
         <v>120</v>
       </c>
@@ -15818,20 +15910,20 @@
       <c r="Y120" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z120" s="21" t="s">
-        <v>868</v>
+      <c r="Z120" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA120" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB120" s="21" t="s">
-        <v>868</v>
+      <c r="AB120" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC120" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="69">
         <v>121</v>
       </c>
@@ -15912,20 +16004,20 @@
       <c r="Y121" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z121" s="21" t="s">
-        <v>868</v>
+      <c r="Z121" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA121" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB121" s="21" t="s">
-        <v>868</v>
+      <c r="AB121" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC121" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="69">
         <v>122</v>
       </c>
@@ -16006,20 +16098,20 @@
       <c r="Y122" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z122" s="21" t="s">
-        <v>868</v>
+      <c r="Z122" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA122" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB122" s="21" t="s">
-        <v>868</v>
+      <c r="AB122" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC122" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="69">
         <v>123</v>
       </c>
@@ -16100,20 +16192,20 @@
       <c r="Y123" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z123" s="21" t="s">
-        <v>868</v>
+      <c r="Z123" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA123" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB123" s="21" t="s">
-        <v>868</v>
+      <c r="AB123" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC123" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="69">
         <v>124</v>
       </c>
@@ -16194,20 +16286,20 @@
       <c r="Y124" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z124" s="21" t="s">
-        <v>868</v>
+      <c r="Z124" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA124" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB124" s="21" t="s">
-        <v>868</v>
+      <c r="AB124" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC124" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="69">
         <v>125</v>
       </c>
@@ -16288,20 +16380,20 @@
       <c r="Y125" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z125" s="21" t="s">
-        <v>868</v>
+      <c r="Z125" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA125" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB125" s="21" t="s">
-        <v>868</v>
+      <c r="AB125" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC125" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="69">
         <v>126</v>
       </c>
@@ -16376,26 +16468,26 @@
         <v>521</v>
       </c>
       <c r="X126" s="71" t="str">
-        <f t="shared" ref="X126:X127" si="26">CONCATENATE("Key-TUB-",A126)</f>
+        <f t="shared" ref="X126:X129" si="26">CONCATENATE("Key-TUB-",A126)</f>
         <v>Key-TUB-126</v>
       </c>
       <c r="Y126" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z126" s="21" t="s">
-        <v>868</v>
+      <c r="Z126" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA126" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB126" s="21" t="s">
-        <v>868</v>
+      <c r="AB126" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC126" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="69">
         <v>127</v>
       </c>
@@ -16476,20 +16568,20 @@
       <c r="Y127" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z127" s="21" t="s">
-        <v>868</v>
+      <c r="Z127" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA127" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB127" s="21" t="s">
-        <v>868</v>
+      <c r="AB127" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC127" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="69">
         <v>128</v>
       </c>
@@ -16524,7 +16616,7 @@
         <v>9</v>
       </c>
       <c r="L128" s="25" t="str">
-        <f t="shared" ref="L128" si="27">SUBSTITUTE(CONCATENATE("", C128), ".", " ")</f>
+        <f t="shared" ref="L128:O129" si="27">SUBSTITUTE(CONCATENATE("", C128), ".", " ")</f>
         <v>De Tubulações</v>
       </c>
       <c r="M128" s="25" t="str">
@@ -16564,70 +16656,169 @@
         <v>521</v>
       </c>
       <c r="X128" s="71" t="str">
-        <f t="shared" ref="X128" si="31">CONCATENATE("Key-TUB-",A128)</f>
+        <f t="shared" si="26"/>
         <v>Key-TUB-128</v>
       </c>
       <c r="Y128" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z128" s="21" t="s">
-        <v>868</v>
+      <c r="Z128" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AA128" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB128" s="21" t="s">
-        <v>868</v>
+      <c r="AB128" s="79" t="s">
+        <v>9</v>
       </c>
       <c r="AC128" s="21" t="s">
         <v>526</v>
       </c>
     </row>
+    <row r="129" spans="1:29" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="69">
+        <v>129</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="C129" s="81" t="s">
+        <v>870</v>
+      </c>
+      <c r="D129" s="81" t="s">
+        <v>871</v>
+      </c>
+      <c r="E129" s="81" t="s">
+        <v>872</v>
+      </c>
+      <c r="F129" s="81" t="s">
+        <v>873</v>
+      </c>
+      <c r="G129" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H129" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I129" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J129" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="K129" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="L129" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>De API</v>
+      </c>
+      <c r="M129" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N129" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Macros</v>
+      </c>
+      <c r="O129" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P129" s="21" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q129" s="77" t="str">
+        <f t="shared" ref="Q129" si="31">_xlfn.TRANSLATE(P129,"pt","es")</f>
+        <v>Aplicación Revit</v>
+      </c>
+      <c r="R129" s="77" t="str">
+        <f t="shared" ref="R129" si="32">_xlfn.TRANSLATE(P129,"pt","en")</f>
+        <v>Revit App</v>
+      </c>
+      <c r="S129" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T129" s="21" t="str">
+        <f t="shared" ref="T129:V129" si="33">SUBSTITUTE(C129, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U129" s="21" t="str">
+        <f t="shared" si="33"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V129" s="78" t="str">
+        <f t="shared" si="33"/>
+        <v>Macros</v>
+      </c>
+      <c r="W129" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="X129" s="71" t="str">
+        <f t="shared" si="26"/>
+        <v>Key-TUB-129</v>
+      </c>
+      <c r="Y129" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z129" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA129" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB129" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC129" s="79" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B128">
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B126 B127:B128 A127:A129">
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F121 F129:F1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="38"/>
+  <conditionalFormatting sqref="F1:F121 F130:F1048576">
+    <cfRule type="duplicateValues" dxfId="26" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F121">
-    <cfRule type="duplicateValues" dxfId="19" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+  <conditionalFormatting sqref="F1:F128 F130:F1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA122:AA128 AC122:AC128">
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="equal">
+  <conditionalFormatting sqref="R1:R121">
+    <cfRule type="cellIs" dxfId="22" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:AA2 AA3:AA121 Z3:Z128 AC2:AC121 AB2:AB128">
-    <cfRule type="cellIs" dxfId="15" priority="39" operator="equal">
+  <conditionalFormatting sqref="Y2:Y128 AA2:AA128 AC2:AC128">
+    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R121">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+  <conditionalFormatting sqref="B129">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F129">
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y122:Y128">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="Q129">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y121">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="R129">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -16637,15 +16828,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -16710,7 +16901,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -16775,7 +16966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -16842,7 +17033,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16858,55 +17049,55 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:AQ61"/>
-  <sheetFormatPr defaultColWidth="5.3046875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="5.28515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3046875" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.69140625" style="34" customWidth="1"/>
-    <col min="3" max="3" width="9.3046875" style="45" customWidth="1"/>
-    <col min="4" max="4" width="7.69140625" style="34" customWidth="1"/>
-    <col min="5" max="5" width="11.69140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.3046875" style="45" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.3828125" style="45" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.3828125" style="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="34" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="45" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="34" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.28515625" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.42578125" style="45" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="45" customWidth="1"/>
-    <col min="10" max="10" width="3.15234375" style="45" customWidth="1"/>
-    <col min="11" max="11" width="3.69140625" style="45" customWidth="1"/>
-    <col min="12" max="12" width="3.69140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.3046875" style="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.69140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.84375" style="34" customWidth="1"/>
-    <col min="16" max="16" width="7.84375" style="45" customWidth="1"/>
-    <col min="17" max="17" width="3.3046875" style="44" customWidth="1"/>
-    <col min="18" max="18" width="7.84375" style="34" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.53515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.140625" style="45" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" style="45" customWidth="1"/>
+    <col min="12" max="12" width="3.7109375" style="45" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.28515625" style="45" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" style="45" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" style="34" customWidth="1"/>
+    <col min="16" max="16" width="7.85546875" style="45" customWidth="1"/>
+    <col min="17" max="17" width="3.28515625" style="44" customWidth="1"/>
+    <col min="18" max="18" width="7.85546875" style="34" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.5703125" style="44" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" style="34" customWidth="1"/>
-    <col min="21" max="21" width="3.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.3046875" style="34" customWidth="1"/>
-    <col min="23" max="23" width="4.15234375" style="34" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.15234375" style="45" customWidth="1"/>
-    <col min="25" max="25" width="3.69140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.69140625" style="45" customWidth="1"/>
-    <col min="27" max="27" width="3.3046875" style="34" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" style="34" customWidth="1"/>
+    <col min="23" max="23" width="4.140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.140625" style="45" customWidth="1"/>
+    <col min="25" max="25" width="3.7109375" style="34" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" style="45" customWidth="1"/>
+    <col min="27" max="27" width="3.28515625" style="34" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9" style="34" customWidth="1"/>
     <col min="29" max="29" width="4" style="44" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="6" style="34" customWidth="1"/>
-    <col min="31" max="31" width="4.53515625" style="44" customWidth="1"/>
-    <col min="32" max="32" width="7.84375" style="34" customWidth="1"/>
-    <col min="33" max="33" width="12.84375" style="34" customWidth="1"/>
-    <col min="34" max="34" width="4.69140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.3046875" style="34" customWidth="1"/>
-    <col min="36" max="36" width="5.3046875" style="45"/>
-    <col min="37" max="37" width="46.69140625" style="34" customWidth="1"/>
+    <col min="31" max="31" width="4.5703125" style="44" customWidth="1"/>
+    <col min="32" max="32" width="7.85546875" style="34" customWidth="1"/>
+    <col min="33" max="33" width="12.85546875" style="34" customWidth="1"/>
+    <col min="34" max="34" width="4.7109375" style="45" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="34" customWidth="1"/>
+    <col min="36" max="36" width="5.28515625" style="45"/>
+    <col min="37" max="37" width="46.7109375" style="34" customWidth="1"/>
     <col min="38" max="38" width="7" style="34" customWidth="1"/>
     <col min="39" max="39" width="12" style="34" customWidth="1"/>
-    <col min="40" max="40" width="5.3046875" style="34"/>
+    <col min="40" max="40" width="5.28515625" style="34"/>
     <col min="41" max="41" width="10" style="34" customWidth="1"/>
-    <col min="42" max="42" width="6.15234375" style="34" customWidth="1"/>
-    <col min="43" max="43" width="11.3046875" style="34" customWidth="1"/>
-    <col min="44" max="16384" width="5.3046875" style="34"/>
+    <col min="42" max="42" width="6.140625" style="34" customWidth="1"/>
+    <col min="43" max="43" width="11.28515625" style="34" customWidth="1"/>
+    <col min="44" max="16384" width="5.28515625" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
@@ -17033,7 +17224,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -17164,7 +17355,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -17295,7 +17486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -17426,7 +17617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -17558,7 +17749,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -17690,7 +17881,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -17822,7 +18013,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -17954,7 +18145,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -18086,7 +18277,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -18218,7 +18409,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -18350,7 +18541,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -18482,7 +18673,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -18614,7 +18805,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="14" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -18746,7 +18937,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="15" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -18878,7 +19069,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -19010,7 +19201,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="17" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -19142,7 +19333,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="18" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -19274,7 +19465,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="19" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -19406,7 +19597,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -19538,7 +19729,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -19670,7 +19861,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="22" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -19802,7 +19993,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="23" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -19934,7 +20125,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="24" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -20066,7 +20257,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="25" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -20198,7 +20389,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="26" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -20330,7 +20521,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="27" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -20462,7 +20653,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="28" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -20594,7 +20785,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="29" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -20726,7 +20917,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="30" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -20858,7 +21049,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="31" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -20990,7 +21181,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="32" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -21122,7 +21313,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="33" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -21254,7 +21445,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="34" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -21386,7 +21577,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="35" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -21518,7 +21709,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="36" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -21650,7 +21841,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="37" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -21782,7 +21973,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>38</v>
       </c>
@@ -21914,7 +22105,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="39" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>39</v>
       </c>
@@ -22046,7 +22237,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="40" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>40</v>
       </c>
@@ -22178,7 +22369,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="41" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>41</v>
       </c>
@@ -22310,7 +22501,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="42" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>42</v>
       </c>
@@ -22442,7 +22633,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="43" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <v>43</v>
       </c>
@@ -22574,7 +22765,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="44" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <v>44</v>
       </c>
@@ -22706,7 +22897,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="45" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <v>45</v>
       </c>
@@ -22838,7 +23029,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="46" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
         <v>46</v>
       </c>
@@ -22970,7 +23161,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="47" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16">
         <v>47</v>
       </c>
@@ -23102,7 +23293,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="48" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
         <v>48</v>
       </c>
@@ -23234,7 +23425,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="49" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16">
         <v>49</v>
       </c>
@@ -23366,7 +23557,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="50" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16">
         <v>50</v>
       </c>
@@ -23498,7 +23689,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="51" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16">
         <v>51</v>
       </c>
@@ -23630,7 +23821,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="52" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16">
         <v>52</v>
       </c>
@@ -23762,7 +23953,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="53" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <v>53</v>
       </c>
@@ -23894,7 +24085,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="54" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
         <v>54</v>
       </c>
@@ -24026,7 +24217,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="55" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
         <v>55</v>
       </c>
@@ -24158,7 +24349,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="56" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <v>56</v>
       </c>
@@ -24290,7 +24481,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="57" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
         <v>57</v>
       </c>
@@ -24422,7 +24613,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="58" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16">
         <v>58</v>
       </c>
@@ -24553,7 +24744,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="59" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
         <v>59</v>
       </c>
@@ -24684,7 +24875,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="60" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
         <v>60</v>
       </c>
@@ -24815,7 +25006,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="61" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
         <v>61</v>
       </c>
@@ -24949,26 +25140,26 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:D1048576 F1:XFD1048576 E2">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58:E61">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E59">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E60">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -24979,15 +25170,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" style="18" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22">
         <v>0</v>
       </c>
@@ -25010,7 +25201,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -25033,7 +25224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -25056,7 +25247,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -25079,7 +25270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -25102,7 +25293,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
         <v>6</v>
       </c>
@@ -25125,7 +25316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
         <v>7</v>
       </c>
@@ -25148,7 +25339,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
         <v>8</v>
       </c>
@@ -25171,7 +25362,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
         <v>9</v>
       </c>
@@ -25194,7 +25385,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
         <v>10</v>
       </c>
@@ -25217,7 +25408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
         <v>11</v>
       </c>
@@ -25240,7 +25431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
         <v>12</v>
       </c>
@@ -25263,7 +25454,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
         <v>13</v>
       </c>
@@ -25286,7 +25477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
         <v>14</v>
       </c>
@@ -25309,7 +25500,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
         <v>15</v>
       </c>
@@ -25335,15 +25526,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B16:G1048576 C2:G15">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/SIS/Ontologia_Tubulacao.xlsx
+++ b/Versão5/SIS/Ontologia_Tubulacao.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABF7F2F-79F6-4C4B-B272-8097D32F6FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0981C0-C444-4623-8D7E-B76F8337DA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -3300,7 +3300,145 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3406,152 +3544,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3987,15 +3979,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="66.5703125" style="26" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="26"/>
+    <col min="1" max="1" width="9.3046875" style="26" customWidth="1"/>
+    <col min="2" max="2" width="66.53515625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -4006,7 +3998,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -4017,7 +4009,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -4028,7 +4020,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -4039,7 +4031,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -4051,7 +4043,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -4063,7 +4055,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -4074,7 +4066,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="55" t="s">
         <v>54</v>
       </c>
@@ -4085,7 +4077,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -4096,7 +4088,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -4107,7 +4099,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -4118,7 +4110,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -4129,7 +4121,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -4140,7 +4132,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -4151,7 +4143,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -4162,7 +4154,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -4173,7 +4165,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -4184,19 +4176,19 @@
         <v>488</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="28">
         <f ca="1">NOW()</f>
-        <v>46260.358396875003</v>
+        <v>46264.570811342594</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -4207,7 +4199,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -4218,7 +4210,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -4229,7 +4221,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -4240,7 +4232,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -4251,7 +4243,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="56" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="56" customFormat="1" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>486</v>
       </c>
@@ -4272,38 +4264,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D59519-D9E5-4433-9132-270924474650}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC129"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="67" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="9.5703125" style="67" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="67" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="101.140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.69140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.53515625" style="67" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.69140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="101.15234375" style="67" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="97" style="67" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="79.140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="67" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="79.15234375" style="67" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.15234375" style="67" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" style="67" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="67" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8" style="67" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="34.7109375" style="67" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.69140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" style="67" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="36" style="67" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="67" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.42578125" style="67" bestFit="1" customWidth="1"/>
-    <col min="30" max="33" width="5.28515625" style="67" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="67"/>
+    <col min="29" max="29" width="12.3828125" style="67" bestFit="1" customWidth="1"/>
+    <col min="30" max="33" width="5.3046875" style="67" customWidth="1"/>
+    <col min="34" max="16384" width="9.15234375" style="67"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="76" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="76" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="73">
         <v>1</v>
       </c>
@@ -4392,7 +4384,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="69">
         <v>2</v>
       </c>
@@ -4489,7 +4481,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="69">
         <v>3</v>
       </c>
@@ -4586,7 +4578,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="69">
         <v>4</v>
       </c>
@@ -4683,7 +4675,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="69">
         <v>5</v>
       </c>
@@ -4780,7 +4772,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="69">
         <v>6</v>
       </c>
@@ -4877,7 +4869,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="69">
         <v>7</v>
       </c>
@@ -4974,7 +4966,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="69">
         <v>8</v>
       </c>
@@ -5071,7 +5063,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="69">
         <v>9</v>
       </c>
@@ -5168,7 +5160,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="69">
         <v>10</v>
       </c>
@@ -5265,7 +5257,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="69">
         <v>11</v>
       </c>
@@ -5362,7 +5354,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="69">
         <v>12</v>
       </c>
@@ -5459,7 +5451,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="69">
         <v>13</v>
       </c>
@@ -5556,7 +5548,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="69">
         <v>14</v>
       </c>
@@ -5653,7 +5645,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="69">
         <v>15</v>
       </c>
@@ -5750,7 +5742,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="69">
         <v>16</v>
       </c>
@@ -5847,7 +5839,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="69">
         <v>17</v>
       </c>
@@ -5944,7 +5936,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="69">
         <v>18</v>
       </c>
@@ -6041,7 +6033,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="69">
         <v>19</v>
       </c>
@@ -6138,7 +6130,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="69">
         <v>20</v>
       </c>
@@ -6235,7 +6227,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="69">
         <v>21</v>
       </c>
@@ -6332,7 +6324,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="69">
         <v>22</v>
       </c>
@@ -6429,7 +6421,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="69">
         <v>23</v>
       </c>
@@ -6526,7 +6518,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="69">
         <v>24</v>
       </c>
@@ -6623,7 +6615,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="69">
         <v>25</v>
       </c>
@@ -6720,7 +6712,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="69">
         <v>26</v>
       </c>
@@ -6817,7 +6809,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="69">
         <v>27</v>
       </c>
@@ -6914,7 +6906,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="69">
         <v>28</v>
       </c>
@@ -7011,7 +7003,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="69">
         <v>29</v>
       </c>
@@ -7108,7 +7100,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="69">
         <v>30</v>
       </c>
@@ -7205,7 +7197,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="69">
         <v>31</v>
       </c>
@@ -7302,7 +7294,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="69">
         <v>32</v>
       </c>
@@ -7399,7 +7391,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="69">
         <v>33</v>
       </c>
@@ -7496,7 +7488,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="69">
         <v>34</v>
       </c>
@@ -7593,7 +7585,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="69">
         <v>35</v>
       </c>
@@ -7690,7 +7682,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="69">
         <v>36</v>
       </c>
@@ -7787,7 +7779,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="69">
         <v>37</v>
       </c>
@@ -7884,7 +7876,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="69">
         <v>38</v>
       </c>
@@ -7981,7 +7973,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="69">
         <v>39</v>
       </c>
@@ -8078,7 +8070,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="69">
         <v>40</v>
       </c>
@@ -8175,7 +8167,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="69">
         <v>41</v>
       </c>
@@ -8272,7 +8264,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="69">
         <v>42</v>
       </c>
@@ -8369,7 +8361,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="69">
         <v>43</v>
       </c>
@@ -8466,7 +8458,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="69">
         <v>44</v>
       </c>
@@ -8563,7 +8555,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="69">
         <v>45</v>
       </c>
@@ -8660,7 +8652,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="69">
         <v>46</v>
       </c>
@@ -8757,7 +8749,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="69">
         <v>47</v>
       </c>
@@ -8854,7 +8846,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="69">
         <v>48</v>
       </c>
@@ -8951,7 +8943,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="69">
         <v>49</v>
       </c>
@@ -9048,7 +9040,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="69">
         <v>50</v>
       </c>
@@ -9145,7 +9137,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="69">
         <v>51</v>
       </c>
@@ -9242,7 +9234,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="69">
         <v>52</v>
       </c>
@@ -9339,7 +9331,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="69">
         <v>53</v>
       </c>
@@ -9436,7 +9428,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="69">
         <v>54</v>
       </c>
@@ -9533,7 +9525,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="69">
         <v>55</v>
       </c>
@@ -9630,7 +9622,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="69">
         <v>56</v>
       </c>
@@ -9727,7 +9719,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="69">
         <v>57</v>
       </c>
@@ -9824,7 +9816,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="69">
         <v>58</v>
       </c>
@@ -9921,7 +9913,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="69">
         <v>59</v>
       </c>
@@ -10018,7 +10010,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="69">
         <v>60</v>
       </c>
@@ -10115,7 +10107,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="69">
         <v>61</v>
       </c>
@@ -10212,7 +10204,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="69">
         <v>62</v>
       </c>
@@ -10309,7 +10301,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="69">
         <v>63</v>
       </c>
@@ -10406,7 +10398,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="69">
         <v>64</v>
       </c>
@@ -10503,7 +10495,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="69">
         <v>65</v>
       </c>
@@ -10600,7 +10592,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="69">
         <v>66</v>
       </c>
@@ -10697,7 +10689,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="69">
         <v>67</v>
       </c>
@@ -10794,7 +10786,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="69">
         <v>68</v>
       </c>
@@ -10891,7 +10883,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="69">
         <v>69</v>
       </c>
@@ -10988,7 +10980,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="69">
         <v>70</v>
       </c>
@@ -11085,7 +11077,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="69">
         <v>71</v>
       </c>
@@ -11182,7 +11174,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="69">
         <v>72</v>
       </c>
@@ -11279,7 +11271,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="69">
         <v>73</v>
       </c>
@@ -11376,7 +11368,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="69">
         <v>74</v>
       </c>
@@ -11473,7 +11465,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="69">
         <v>75</v>
       </c>
@@ -11570,7 +11562,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="69">
         <v>76</v>
       </c>
@@ -11667,7 +11659,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="69">
         <v>77</v>
       </c>
@@ -11764,7 +11756,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="69">
         <v>78</v>
       </c>
@@ -11861,7 +11853,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="69">
         <v>79</v>
       </c>
@@ -11958,7 +11950,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="69">
         <v>80</v>
       </c>
@@ -12055,7 +12047,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="69">
         <v>81</v>
       </c>
@@ -12152,7 +12144,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="69">
         <v>82</v>
       </c>
@@ -12249,7 +12241,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="69">
         <v>83</v>
       </c>
@@ -12346,7 +12338,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="69">
         <v>84</v>
       </c>
@@ -12443,7 +12435,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="69">
         <v>85</v>
       </c>
@@ -12540,7 +12532,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="69">
         <v>86</v>
       </c>
@@ -12637,7 +12629,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="69">
         <v>87</v>
       </c>
@@ -12734,7 +12726,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="69">
         <v>88</v>
       </c>
@@ -12831,7 +12823,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="69">
         <v>89</v>
       </c>
@@ -12928,7 +12920,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="69">
         <v>90</v>
       </c>
@@ -13025,7 +13017,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="69">
         <v>91</v>
       </c>
@@ -13122,7 +13114,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="69">
         <v>92</v>
       </c>
@@ -13219,7 +13211,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="69">
         <v>93</v>
       </c>
@@ -13316,7 +13308,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="69">
         <v>94</v>
       </c>
@@ -13413,7 +13405,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="69">
         <v>95</v>
       </c>
@@ -13510,7 +13502,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="69">
         <v>96</v>
       </c>
@@ -13607,7 +13599,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="69">
         <v>97</v>
       </c>
@@ -13704,7 +13696,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="69">
         <v>98</v>
       </c>
@@ -13801,7 +13793,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="69">
         <v>99</v>
       </c>
@@ -13898,7 +13890,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="69">
         <v>100</v>
       </c>
@@ -13995,7 +13987,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="69">
         <v>101</v>
       </c>
@@ -14092,7 +14084,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="69">
         <v>102</v>
       </c>
@@ -14189,7 +14181,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="69">
         <v>103</v>
       </c>
@@ -14286,7 +14278,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="69">
         <v>104</v>
       </c>
@@ -14383,7 +14375,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="69">
         <v>105</v>
       </c>
@@ -14480,7 +14472,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="69">
         <v>106</v>
       </c>
@@ -14577,7 +14569,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="69">
         <v>107</v>
       </c>
@@ -14674,7 +14666,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="69">
         <v>108</v>
       </c>
@@ -14771,7 +14763,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="69">
         <v>109</v>
       </c>
@@ -14868,7 +14860,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="69">
         <v>110</v>
       </c>
@@ -14965,7 +14957,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="69">
         <v>111</v>
       </c>
@@ -15062,7 +15054,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="69">
         <v>112</v>
       </c>
@@ -15159,7 +15151,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="69">
         <v>113</v>
       </c>
@@ -15256,7 +15248,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="69">
         <v>114</v>
       </c>
@@ -15353,7 +15345,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="69">
         <v>115</v>
       </c>
@@ -15450,7 +15442,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="69">
         <v>116</v>
       </c>
@@ -15547,7 +15539,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="69">
         <v>117</v>
       </c>
@@ -15641,7 +15633,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="69">
         <v>118</v>
       </c>
@@ -15735,7 +15727,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="69">
         <v>119</v>
       </c>
@@ -15829,7 +15821,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="69">
         <v>120</v>
       </c>
@@ -15923,7 +15915,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="69">
         <v>121</v>
       </c>
@@ -16017,7 +16009,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="69">
         <v>122</v>
       </c>
@@ -16111,7 +16103,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="69">
         <v>123</v>
       </c>
@@ -16205,7 +16197,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="69">
         <v>124</v>
       </c>
@@ -16299,7 +16291,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="69">
         <v>125</v>
       </c>
@@ -16393,7 +16385,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="69">
         <v>126</v>
       </c>
@@ -16487,7 +16479,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="69">
         <v>127</v>
       </c>
@@ -16581,7 +16573,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="69">
         <v>128</v>
       </c>
@@ -16675,7 +16667,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="129" spans="1:29" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:29" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="69">
         <v>129</v>
       </c>
@@ -16686,10 +16678,10 @@
         <v>870</v>
       </c>
       <c r="D129" s="81" t="s">
+        <v>872</v>
+      </c>
+      <c r="E129" s="81" t="s">
         <v>871</v>
-      </c>
-      <c r="E129" s="81" t="s">
-        <v>872</v>
       </c>
       <c r="F129" s="81" t="s">
         <v>873</v>
@@ -16715,11 +16707,11 @@
       </c>
       <c r="M129" s="25" t="str">
         <f t="shared" si="27"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N129" s="25" t="str">
         <f t="shared" si="27"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O129" s="25" t="str">
         <f t="shared" si="27"/>
@@ -16745,11 +16737,11 @@
       </c>
       <c r="U129" s="21" t="str">
         <f t="shared" si="33"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V129" s="78" t="str">
         <f t="shared" si="33"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W129" s="21" t="s">
         <v>521</v>
@@ -16775,50 +16767,45 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B126 B127:B128 A127:A129">
-    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+  <conditionalFormatting sqref="A2:B129">
+    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F121 F130:F1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F121">
-    <cfRule type="duplicateValues" dxfId="25" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F128 F130:F1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F129">
+    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q129">
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R121">
-    <cfRule type="cellIs" dxfId="22" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R129">
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y128 AA2:AA128 AC2:AC128">
-    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B129">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F129">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q129">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R129">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -16828,15 +16815,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -16901,7 +16888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -16966,7 +16953,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -17033,7 +17020,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17049,55 +17036,55 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:AQ61"/>
-  <sheetFormatPr defaultColWidth="5.28515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="5.3046875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="34" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" style="45" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="34" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" style="45" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.42578125" style="45" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3046875" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69140625" style="34" customWidth="1"/>
+    <col min="3" max="3" width="9.3046875" style="45" customWidth="1"/>
+    <col min="4" max="4" width="7.69140625" style="34" customWidth="1"/>
+    <col min="5" max="5" width="11.69140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.3046875" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.3828125" style="45" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.3828125" style="45" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="45" customWidth="1"/>
-    <col min="10" max="10" width="3.140625" style="45" customWidth="1"/>
-    <col min="11" max="11" width="3.7109375" style="45" customWidth="1"/>
-    <col min="12" max="12" width="3.7109375" style="45" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.28515625" style="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" style="45" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.85546875" style="34" customWidth="1"/>
-    <col min="16" max="16" width="7.85546875" style="45" customWidth="1"/>
-    <col min="17" max="17" width="3.28515625" style="44" customWidth="1"/>
-    <col min="18" max="18" width="7.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.5703125" style="44" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.15234375" style="45" customWidth="1"/>
+    <col min="11" max="11" width="3.69140625" style="45" customWidth="1"/>
+    <col min="12" max="12" width="3.69140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.3046875" style="45" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.69140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.84375" style="34" customWidth="1"/>
+    <col min="16" max="16" width="7.84375" style="45" customWidth="1"/>
+    <col min="17" max="17" width="3.3046875" style="44" customWidth="1"/>
+    <col min="18" max="18" width="7.84375" style="34" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.53515625" style="44" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" style="34" customWidth="1"/>
-    <col min="21" max="21" width="3.28515625" style="44" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.28515625" style="34" customWidth="1"/>
-    <col min="23" max="23" width="4.140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.140625" style="45" customWidth="1"/>
-    <col min="25" max="25" width="3.7109375" style="34" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" style="45" customWidth="1"/>
-    <col min="27" max="27" width="3.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.3046875" style="44" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.3046875" style="34" customWidth="1"/>
+    <col min="23" max="23" width="4.15234375" style="34" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.15234375" style="45" customWidth="1"/>
+    <col min="25" max="25" width="3.69140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.69140625" style="45" customWidth="1"/>
+    <col min="27" max="27" width="3.3046875" style="34" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9" style="34" customWidth="1"/>
     <col min="29" max="29" width="4" style="44" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="6" style="34" customWidth="1"/>
-    <col min="31" max="31" width="4.5703125" style="44" customWidth="1"/>
-    <col min="32" max="32" width="7.85546875" style="34" customWidth="1"/>
-    <col min="33" max="33" width="12.85546875" style="34" customWidth="1"/>
-    <col min="34" max="34" width="4.7109375" style="45" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="34" customWidth="1"/>
-    <col min="36" max="36" width="5.28515625" style="45"/>
-    <col min="37" max="37" width="46.7109375" style="34" customWidth="1"/>
+    <col min="31" max="31" width="4.53515625" style="44" customWidth="1"/>
+    <col min="32" max="32" width="7.84375" style="34" customWidth="1"/>
+    <col min="33" max="33" width="12.84375" style="34" customWidth="1"/>
+    <col min="34" max="34" width="4.69140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.3046875" style="34" customWidth="1"/>
+    <col min="36" max="36" width="5.3046875" style="45"/>
+    <col min="37" max="37" width="46.69140625" style="34" customWidth="1"/>
     <col min="38" max="38" width="7" style="34" customWidth="1"/>
     <col min="39" max="39" width="12" style="34" customWidth="1"/>
-    <col min="40" max="40" width="5.28515625" style="34"/>
+    <col min="40" max="40" width="5.3046875" style="34"/>
     <col min="41" max="41" width="10" style="34" customWidth="1"/>
-    <col min="42" max="42" width="6.140625" style="34" customWidth="1"/>
-    <col min="43" max="43" width="11.28515625" style="34" customWidth="1"/>
-    <col min="44" max="16384" width="5.28515625" style="34"/>
+    <col min="42" max="42" width="6.15234375" style="34" customWidth="1"/>
+    <col min="43" max="43" width="11.3046875" style="34" customWidth="1"/>
+    <col min="44" max="16384" width="5.3046875" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
@@ -17224,7 +17211,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -17355,7 +17342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -17486,7 +17473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -17617,7 +17604,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -17749,7 +17736,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -17881,7 +17868,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -18013,7 +18000,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -18145,7 +18132,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -18277,7 +18264,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -18409,7 +18396,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -18541,7 +18528,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -18673,7 +18660,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -18805,7 +18792,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="14" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -18937,7 +18924,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="15" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -19069,7 +19056,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -19201,7 +19188,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="17" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -19333,7 +19320,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="18" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -19465,7 +19452,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="19" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -19597,7 +19584,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -19729,7 +19716,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -19861,7 +19848,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="22" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -19993,7 +19980,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="23" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -20125,7 +20112,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="24" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -20257,7 +20244,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="25" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -20389,7 +20376,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="26" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -20521,7 +20508,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="27" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -20653,7 +20640,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="28" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -20785,7 +20772,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="29" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -20917,7 +20904,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="30" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -21049,7 +21036,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="31" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -21181,7 +21168,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="32" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -21313,7 +21300,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="33" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -21445,7 +21432,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="34" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -21577,7 +21564,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="35" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -21709,7 +21696,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="36" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -21841,7 +21828,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="37" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -21973,7 +21960,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="16">
         <v>38</v>
       </c>
@@ -22105,7 +22092,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="39" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="16">
         <v>39</v>
       </c>
@@ -22237,7 +22224,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="40" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="16">
         <v>40</v>
       </c>
@@ -22369,7 +22356,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="41" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="16">
         <v>41</v>
       </c>
@@ -22501,7 +22488,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="42" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="16">
         <v>42</v>
       </c>
@@ -22633,7 +22620,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="43" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="16">
         <v>43</v>
       </c>
@@ -22765,7 +22752,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="44" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="16">
         <v>44</v>
       </c>
@@ -22897,7 +22884,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="45" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="16">
         <v>45</v>
       </c>
@@ -23029,7 +23016,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="46" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="16">
         <v>46</v>
       </c>
@@ -23161,7 +23148,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="47" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="16">
         <v>47</v>
       </c>
@@ -23293,7 +23280,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="48" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="16">
         <v>48</v>
       </c>
@@ -23425,7 +23412,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="49" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="16">
         <v>49</v>
       </c>
@@ -23557,7 +23544,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="50" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="16">
         <v>50</v>
       </c>
@@ -23689,7 +23676,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="51" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="16">
         <v>51</v>
       </c>
@@ -23821,7 +23808,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="52" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="16">
         <v>52</v>
       </c>
@@ -23953,7 +23940,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="53" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="16">
         <v>53</v>
       </c>
@@ -24085,7 +24072,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="54" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="16">
         <v>54</v>
       </c>
@@ -24217,7 +24204,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="55" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="16">
         <v>55</v>
       </c>
@@ -24349,7 +24336,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="56" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="16">
         <v>56</v>
       </c>
@@ -24481,7 +24468,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="57" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="16">
         <v>57</v>
       </c>
@@ -24613,7 +24600,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="58" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="16">
         <v>58</v>
       </c>
@@ -24744,7 +24731,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="59" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="16">
         <v>59</v>
       </c>
@@ -24875,7 +24862,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="60" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="16">
         <v>60</v>
       </c>
@@ -25006,7 +24993,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="61" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="16">
         <v>61</v>
       </c>
@@ -25140,26 +25127,26 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:D1048576 F1:XFD1048576 E2">
-    <cfRule type="cellIs" dxfId="19" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58:E61">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E59">
-    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E60">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25170,15 +25157,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" style="18" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22">
         <v>0</v>
       </c>
@@ -25201,7 +25188,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -25224,7 +25211,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -25247,7 +25234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -25270,7 +25257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -25293,7 +25280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="23">
         <v>6</v>
       </c>
@@ -25316,7 +25303,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="23">
         <v>7</v>
       </c>
@@ -25339,7 +25326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="23">
         <v>8</v>
       </c>
@@ -25362,7 +25349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="23">
         <v>9</v>
       </c>
@@ -25385,7 +25372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="23">
         <v>10</v>
       </c>
@@ -25408,7 +25395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="23">
         <v>11</v>
       </c>
@@ -25431,7 +25418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="23">
         <v>12</v>
       </c>
@@ -25454,7 +25441,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="23">
         <v>13</v>
       </c>
@@ -25477,7 +25464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="23">
         <v>14</v>
       </c>
@@ -25500,7 +25487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="23">
         <v>15</v>
       </c>
@@ -25526,15 +25513,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B16:G1048576 C2:G15">
-    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/SIS/Ontologia_Tubulacao.xlsx
+++ b/Versão5/SIS/Ontologia_Tubulacao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0981C0-C444-4623-8D7E-B76F8337DA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1121BF70-FB3B-4AA8-B50D-5BCD785E06D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4942" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5157" uniqueCount="895">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2693,10 +2693,70 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -3053,7 +3113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3282,9 +3342,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3300,7 +3357,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="19">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3401,81 +3458,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3979,15 +3966,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="66.53515625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="26"/>
+    <col min="1" max="1" width="9.28515625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="66.5703125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -3998,7 +3985,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -4009,7 +3996,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -4020,7 +4007,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -4031,7 +4018,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -4043,7 +4030,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -4055,7 +4042,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -4066,7 +4053,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
         <v>54</v>
       </c>
@@ -4077,7 +4064,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -4088,7 +4075,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -4099,7 +4086,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -4110,7 +4097,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -4121,7 +4108,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -4132,7 +4119,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -4143,7 +4130,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -4154,7 +4141,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -4165,7 +4152,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -4176,19 +4163,19 @@
         <v>488</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="28">
         <f ca="1">NOW()</f>
-        <v>46264.570811342594</v>
+        <v>46268.70087453704</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -4199,7 +4186,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -4210,7 +4197,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -4221,7 +4208,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -4232,7 +4219,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -4243,7 +4230,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="56" customFormat="1" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="56" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>486</v>
       </c>
@@ -4263,39 +4250,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D59519-D9E5-4433-9132-270924474650}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC129"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD133"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.84375" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.69140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.84375" style="67" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.84375" style="67" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="9.53515625" style="67" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.84375" style="67" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.69140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.84375" style="67" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.84375" style="67" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="101.15234375" style="67" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.5703125" style="67" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="101.140625" style="67" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="97" style="67" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="79.15234375" style="67" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.15234375" style="67" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="79.140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.140625" style="67" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" style="67" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.84375" style="67" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.69140625" style="67" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="67" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8" style="67" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="34.69140625" style="67" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.7109375" style="67" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="67" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="36" style="67" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="67" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.3828125" style="67" bestFit="1" customWidth="1"/>
-    <col min="30" max="33" width="5.3046875" style="67" customWidth="1"/>
-    <col min="34" max="16384" width="9.15234375" style="67"/>
+    <col min="29" max="29" width="12.42578125" style="67" bestFit="1" customWidth="1"/>
+    <col min="30" max="33" width="5.28515625" style="67" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="67"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="76" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" s="76" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="73">
         <v>1</v>
       </c>
@@ -4383,8 +4370,11 @@
       <c r="AC1" s="53" t="s">
         <v>483</v>
       </c>
+      <c r="AD1" s="53" t="s">
+        <v>894</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="69">
         <v>2</v>
       </c>
@@ -4468,20 +4458,23 @@
       <c r="Y2" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z2" s="79" t="s">
+      <c r="Z2" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB2" s="79" t="s">
+      <c r="AB2" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="21" t="s">
         <v>570</v>
       </c>
+      <c r="AD2" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="69">
         <v>3</v>
       </c>
@@ -4565,20 +4558,23 @@
       <c r="Y3" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z3" s="79" t="s">
+      <c r="Z3" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB3" s="79" t="s">
+      <c r="AB3" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="21" t="s">
         <v>569</v>
       </c>
+      <c r="AD3" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="69">
         <v>4</v>
       </c>
@@ -4662,20 +4658,23 @@
       <c r="Y4" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z4" s="79" t="s">
+      <c r="Z4" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB4" s="79" t="s">
+      <c r="AB4" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="21" t="s">
         <v>569</v>
       </c>
+      <c r="AD4" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="69">
         <v>5</v>
       </c>
@@ -4759,20 +4758,23 @@
       <c r="Y5" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z5" s="79" t="s">
+      <c r="Z5" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB5" s="79" t="s">
+      <c r="AB5" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="21" t="s">
         <v>572</v>
       </c>
+      <c r="AD5" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="69">
         <v>6</v>
       </c>
@@ -4856,20 +4858,23 @@
       <c r="Y6" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z6" s="79" t="s">
+      <c r="Z6" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB6" s="79" t="s">
+      <c r="AB6" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="21" t="s">
         <v>573</v>
       </c>
+      <c r="AD6" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="69">
         <v>7</v>
       </c>
@@ -4953,20 +4958,23 @@
       <c r="Y7" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z7" s="79" t="s">
+      <c r="Z7" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB7" s="79" t="s">
+      <c r="AB7" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="21" t="s">
         <v>574</v>
       </c>
+      <c r="AD7" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="69">
         <v>8</v>
       </c>
@@ -5050,20 +5058,23 @@
       <c r="Y8" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="Z8" s="79" t="s">
+      <c r="Z8" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="AB8" s="79" t="s">
+      <c r="AB8" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="21" t="s">
         <v>571</v>
       </c>
+      <c r="AD8" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="69">
         <v>9</v>
       </c>
@@ -5147,20 +5158,23 @@
       <c r="Y9" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z9" s="79" t="s">
+      <c r="Z9" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="68" t="s">
         <v>525</v>
       </c>
-      <c r="AB9" s="79" t="s">
+      <c r="AB9" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD9" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="69">
         <v>10</v>
       </c>
@@ -5244,20 +5258,23 @@
       <c r="Y10" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z10" s="79" t="s">
+      <c r="Z10" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="68" t="s">
         <v>527</v>
       </c>
-      <c r="AB10" s="79" t="s">
+      <c r="AB10" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD10" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69">
         <v>11</v>
       </c>
@@ -5341,20 +5358,23 @@
       <c r="Y11" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z11" s="79" t="s">
+      <c r="Z11" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="68" t="s">
         <v>528</v>
       </c>
-      <c r="AB11" s="79" t="s">
+      <c r="AB11" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD11" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="69">
         <v>12</v>
       </c>
@@ -5438,20 +5458,23 @@
       <c r="Y12" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z12" s="79" t="s">
+      <c r="Z12" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="68" t="s">
         <v>529</v>
       </c>
-      <c r="AB12" s="79" t="s">
+      <c r="AB12" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD12" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="69">
         <v>13</v>
       </c>
@@ -5535,20 +5558,23 @@
       <c r="Y13" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z13" s="79" t="s">
+      <c r="Z13" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="68" t="s">
         <v>530</v>
       </c>
-      <c r="AB13" s="79" t="s">
+      <c r="AB13" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD13" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="69">
         <v>14</v>
       </c>
@@ -5632,20 +5658,23 @@
       <c r="Y14" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z14" s="79" t="s">
+      <c r="Z14" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="68" t="s">
         <v>531</v>
       </c>
-      <c r="AB14" s="79" t="s">
+      <c r="AB14" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD14" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="69">
         <v>15</v>
       </c>
@@ -5729,20 +5758,23 @@
       <c r="Y15" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z15" s="79" t="s">
+      <c r="Z15" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="68" t="s">
         <v>532</v>
       </c>
-      <c r="AB15" s="79" t="s">
+      <c r="AB15" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD15" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="69">
         <v>16</v>
       </c>
@@ -5826,20 +5858,23 @@
       <c r="Y16" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z16" s="79" t="s">
+      <c r="Z16" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="68" t="s">
         <v>533</v>
       </c>
-      <c r="AB16" s="79" t="s">
+      <c r="AB16" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD16" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="69">
         <v>17</v>
       </c>
@@ -5923,20 +5958,23 @@
       <c r="Y17" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z17" s="79" t="s">
+      <c r="Z17" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="68" t="s">
         <v>534</v>
       </c>
-      <c r="AB17" s="79" t="s">
+      <c r="AB17" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD17" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="69">
         <v>18</v>
       </c>
@@ -6020,20 +6058,23 @@
       <c r="Y18" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z18" s="79" t="s">
+      <c r="Z18" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB18" s="79" t="s">
+      <c r="AB18" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD18" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="69">
         <v>19</v>
       </c>
@@ -6117,20 +6158,23 @@
       <c r="Y19" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z19" s="79" t="s">
+      <c r="Z19" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB19" s="79" t="s">
+      <c r="AB19" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD19" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="69">
         <v>20</v>
       </c>
@@ -6214,20 +6258,23 @@
       <c r="Y20" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z20" s="79" t="s">
+      <c r="Z20" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB20" s="79" t="s">
+      <c r="AB20" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD20" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="69">
         <v>21</v>
       </c>
@@ -6311,20 +6358,23 @@
       <c r="Y21" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z21" s="79" t="s">
+      <c r="Z21" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB21" s="79" t="s">
+      <c r="AB21" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC21" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD21" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="69">
         <v>22</v>
       </c>
@@ -6408,20 +6458,23 @@
       <c r="Y22" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z22" s="79" t="s">
+      <c r="Z22" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="AB22" s="79" t="s">
+      <c r="AB22" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC22" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD22" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="69">
         <v>23</v>
       </c>
@@ -6505,20 +6558,23 @@
       <c r="Y23" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z23" s="79" t="s">
+      <c r="Z23" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="68" t="s">
         <v>538</v>
       </c>
-      <c r="AB23" s="79" t="s">
+      <c r="AB23" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC23" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD23" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="69">
         <v>24</v>
       </c>
@@ -6602,20 +6658,23 @@
       <c r="Y24" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z24" s="79" t="s">
+      <c r="Z24" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="68" t="s">
         <v>539</v>
       </c>
-      <c r="AB24" s="79" t="s">
+      <c r="AB24" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC24" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD24" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="69">
         <v>25</v>
       </c>
@@ -6699,20 +6758,23 @@
       <c r="Y25" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z25" s="79" t="s">
+      <c r="Z25" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="68" t="s">
         <v>540</v>
       </c>
-      <c r="AB25" s="79" t="s">
+      <c r="AB25" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC25" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD25" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="69">
         <v>26</v>
       </c>
@@ -6796,20 +6858,23 @@
       <c r="Y26" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z26" s="79" t="s">
+      <c r="Z26" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA26" s="68" t="s">
         <v>540</v>
       </c>
-      <c r="AB26" s="79" t="s">
+      <c r="AB26" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC26" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD26" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="69">
         <v>27</v>
       </c>
@@ -6893,20 +6958,23 @@
       <c r="Y27" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z27" s="79" t="s">
+      <c r="Z27" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA27" s="68" t="s">
         <v>541</v>
       </c>
-      <c r="AB27" s="79" t="s">
+      <c r="AB27" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC27" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD27" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="69">
         <v>28</v>
       </c>
@@ -6990,20 +7058,23 @@
       <c r="Y28" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z28" s="79" t="s">
+      <c r="Z28" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA28" s="68" t="s">
         <v>542</v>
       </c>
-      <c r="AB28" s="79" t="s">
+      <c r="AB28" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC28" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD28" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="69">
         <v>29</v>
       </c>
@@ -7087,20 +7158,23 @@
       <c r="Y29" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z29" s="79" t="s">
+      <c r="Z29" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA29" s="68" t="s">
         <v>543</v>
       </c>
-      <c r="AB29" s="79" t="s">
+      <c r="AB29" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC29" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD29" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="69">
         <v>30</v>
       </c>
@@ -7184,20 +7258,23 @@
       <c r="Y30" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z30" s="79" t="s">
+      <c r="Z30" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA30" s="68" t="s">
         <v>540</v>
       </c>
-      <c r="AB30" s="79" t="s">
+      <c r="AB30" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC30" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD30" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="69">
         <v>31</v>
       </c>
@@ -7281,20 +7358,23 @@
       <c r="Y31" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z31" s="79" t="s">
+      <c r="Z31" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA31" s="68" t="s">
         <v>541</v>
       </c>
-      <c r="AB31" s="79" t="s">
+      <c r="AB31" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC31" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD31" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="69">
         <v>32</v>
       </c>
@@ -7378,20 +7458,23 @@
       <c r="Y32" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z32" s="79" t="s">
+      <c r="Z32" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA32" s="68" t="s">
         <v>542</v>
       </c>
-      <c r="AB32" s="79" t="s">
+      <c r="AB32" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC32" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD32" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="69">
         <v>33</v>
       </c>
@@ -7475,20 +7558,23 @@
       <c r="Y33" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z33" s="79" t="s">
+      <c r="Z33" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA33" s="68" t="s">
         <v>543</v>
       </c>
-      <c r="AB33" s="79" t="s">
+      <c r="AB33" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC33" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD33" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="69">
         <v>34</v>
       </c>
@@ -7572,20 +7658,23 @@
       <c r="Y34" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z34" s="79" t="s">
+      <c r="Z34" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="AB34" s="79" t="s">
+      <c r="AB34" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC34" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD34" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="69">
         <v>35</v>
       </c>
@@ -7669,20 +7758,23 @@
       <c r="Y35" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z35" s="79" t="s">
+      <c r="Z35" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="68" t="s">
         <v>544</v>
       </c>
-      <c r="AB35" s="79" t="s">
+      <c r="AB35" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC35" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD35" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="69">
         <v>36</v>
       </c>
@@ -7766,20 +7858,23 @@
       <c r="Y36" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z36" s="79" t="s">
+      <c r="Z36" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA36" s="68" t="s">
         <v>545</v>
       </c>
-      <c r="AB36" s="79" t="s">
+      <c r="AB36" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC36" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD36" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="69">
         <v>37</v>
       </c>
@@ -7863,20 +7958,23 @@
       <c r="Y37" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z37" s="79" t="s">
+      <c r="Z37" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA37" s="68" t="s">
         <v>546</v>
       </c>
-      <c r="AB37" s="79" t="s">
+      <c r="AB37" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC37" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD37" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="69">
         <v>38</v>
       </c>
@@ -7960,20 +8058,23 @@
       <c r="Y38" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z38" s="79" t="s">
+      <c r="Z38" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA38" s="68" t="s">
         <v>547</v>
       </c>
-      <c r="AB38" s="79" t="s">
+      <c r="AB38" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC38" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD38" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="69">
         <v>39</v>
       </c>
@@ -8057,20 +8158,23 @@
       <c r="Y39" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z39" s="79" t="s">
+      <c r="Z39" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA39" s="68" t="s">
         <v>541</v>
       </c>
-      <c r="AB39" s="79" t="s">
+      <c r="AB39" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC39" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD39" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="69">
         <v>40</v>
       </c>
@@ -8154,20 +8258,23 @@
       <c r="Y40" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z40" s="79" t="s">
+      <c r="Z40" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA40" s="68" t="s">
         <v>533</v>
       </c>
-      <c r="AB40" s="79" t="s">
+      <c r="AB40" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC40" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD40" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="69">
         <v>41</v>
       </c>
@@ -8251,20 +8358,23 @@
       <c r="Y41" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z41" s="79" t="s">
+      <c r="Z41" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA41" s="68" t="s">
         <v>533</v>
       </c>
-      <c r="AB41" s="79" t="s">
+      <c r="AB41" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC41" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD41" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="69">
         <v>42</v>
       </c>
@@ -8348,20 +8458,23 @@
       <c r="Y42" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z42" s="79" t="s">
+      <c r="Z42" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA42" s="68" t="s">
         <v>548</v>
       </c>
-      <c r="AB42" s="79" t="s">
+      <c r="AB42" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC42" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD42" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="69">
         <v>43</v>
       </c>
@@ -8445,20 +8558,23 @@
       <c r="Y43" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="Z43" s="79" t="s">
+      <c r="Z43" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA43" s="68" t="s">
         <v>549</v>
       </c>
-      <c r="AB43" s="79" t="s">
+      <c r="AB43" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC43" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD43" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="69">
         <v>44</v>
       </c>
@@ -8542,20 +8658,23 @@
       <c r="Y44" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z44" s="79" t="s">
+      <c r="Z44" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA44" s="68" t="s">
         <v>550</v>
       </c>
-      <c r="AB44" s="79" t="s">
+      <c r="AB44" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC44" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD44" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="69">
         <v>45</v>
       </c>
@@ -8639,20 +8758,23 @@
       <c r="Y45" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="Z45" s="79" t="s">
+      <c r="Z45" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA45" s="68" t="s">
         <v>551</v>
       </c>
-      <c r="AB45" s="79" t="s">
+      <c r="AB45" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC45" s="21" t="s">
         <v>537</v>
       </c>
+      <c r="AD45" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="69">
         <v>46</v>
       </c>
@@ -8736,20 +8858,23 @@
       <c r="Y46" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z46" s="79" t="s">
+      <c r="Z46" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA46" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB46" s="79" t="s">
+      <c r="AB46" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC46" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD46" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="69">
         <v>47</v>
       </c>
@@ -8833,20 +8958,23 @@
       <c r="Y47" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z47" s="79" t="s">
+      <c r="Z47" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA47" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB47" s="79" t="s">
+      <c r="AB47" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC47" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD47" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="69">
         <v>48</v>
       </c>
@@ -8930,20 +9058,23 @@
       <c r="Y48" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z48" s="79" t="s">
+      <c r="Z48" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA48" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB48" s="79" t="s">
+      <c r="AB48" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC48" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD48" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="69">
         <v>49</v>
       </c>
@@ -9027,20 +9158,23 @@
       <c r="Y49" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z49" s="79" t="s">
+      <c r="Z49" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA49" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB49" s="79" t="s">
+      <c r="AB49" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC49" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD49" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="69">
         <v>50</v>
       </c>
@@ -9124,20 +9258,23 @@
       <c r="Y50" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z50" s="79" t="s">
+      <c r="Z50" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA50" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB50" s="79" t="s">
+      <c r="AB50" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC50" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD50" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="69">
         <v>51</v>
       </c>
@@ -9221,20 +9358,23 @@
       <c r="Y51" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z51" s="79" t="s">
+      <c r="Z51" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA51" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB51" s="79" t="s">
+      <c r="AB51" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC51" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD51" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="69">
         <v>52</v>
       </c>
@@ -9318,20 +9458,23 @@
       <c r="Y52" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z52" s="79" t="s">
+      <c r="Z52" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA52" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB52" s="79" t="s">
+      <c r="AB52" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC52" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD52" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="69">
         <v>53</v>
       </c>
@@ -9415,20 +9558,23 @@
       <c r="Y53" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z53" s="79" t="s">
+      <c r="Z53" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA53" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB53" s="79" t="s">
+      <c r="AB53" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC53" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD53" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="69">
         <v>54</v>
       </c>
@@ -9512,20 +9658,23 @@
       <c r="Y54" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z54" s="79" t="s">
+      <c r="Z54" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA54" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB54" s="79" t="s">
+      <c r="AB54" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC54" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD54" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="69">
         <v>55</v>
       </c>
@@ -9609,20 +9758,23 @@
       <c r="Y55" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="Z55" s="79" t="s">
+      <c r="Z55" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA55" s="21" t="s">
         <v>553</v>
       </c>
-      <c r="AB55" s="79" t="s">
+      <c r="AB55" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC55" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD55" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="69">
         <v>56</v>
       </c>
@@ -9706,20 +9858,23 @@
       <c r="Y56" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z56" s="79" t="s">
+      <c r="Z56" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA56" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB56" s="79" t="s">
+      <c r="AB56" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC56" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD56" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="69">
         <v>57</v>
       </c>
@@ -9803,20 +9958,23 @@
       <c r="Y57" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z57" s="79" t="s">
+      <c r="Z57" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA57" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB57" s="79" t="s">
+      <c r="AB57" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC57" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD57" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="69">
         <v>58</v>
       </c>
@@ -9900,20 +10058,23 @@
       <c r="Y58" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z58" s="79" t="s">
+      <c r="Z58" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA58" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB58" s="79" t="s">
+      <c r="AB58" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC58" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD58" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="69">
         <v>59</v>
       </c>
@@ -9997,20 +10158,23 @@
       <c r="Y59" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z59" s="79" t="s">
+      <c r="Z59" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA59" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB59" s="79" t="s">
+      <c r="AB59" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC59" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD59" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="69">
         <v>60</v>
       </c>
@@ -10094,20 +10258,23 @@
       <c r="Y60" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z60" s="79" t="s">
+      <c r="Z60" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA60" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB60" s="79" t="s">
+      <c r="AB60" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC60" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD60" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="69">
         <v>61</v>
       </c>
@@ -10191,20 +10358,23 @@
       <c r="Y61" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z61" s="79" t="s">
+      <c r="Z61" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA61" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB61" s="79" t="s">
+      <c r="AB61" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC61" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD61" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="69">
         <v>62</v>
       </c>
@@ -10288,20 +10458,23 @@
       <c r="Y62" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z62" s="79" t="s">
+      <c r="Z62" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA62" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB62" s="79" t="s">
+      <c r="AB62" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC62" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD62" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="69">
         <v>63</v>
       </c>
@@ -10385,20 +10558,23 @@
       <c r="Y63" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z63" s="79" t="s">
+      <c r="Z63" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA63" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB63" s="79" t="s">
+      <c r="AB63" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC63" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD63" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="69">
         <v>64</v>
       </c>
@@ -10482,20 +10658,23 @@
       <c r="Y64" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z64" s="79" t="s">
+      <c r="Z64" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA64" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB64" s="79" t="s">
+      <c r="AB64" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC64" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD64" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="69">
         <v>65</v>
       </c>
@@ -10579,20 +10758,23 @@
       <c r="Y65" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z65" s="79" t="s">
+      <c r="Z65" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA65" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB65" s="79" t="s">
+      <c r="AB65" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC65" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD65" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="69">
         <v>66</v>
       </c>
@@ -10676,20 +10858,23 @@
       <c r="Y66" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z66" s="79" t="s">
+      <c r="Z66" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA66" s="21" t="s">
         <v>555</v>
       </c>
-      <c r="AB66" s="79" t="s">
+      <c r="AB66" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC66" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD66" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="69">
         <v>67</v>
       </c>
@@ -10773,20 +10958,23 @@
       <c r="Y67" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z67" s="79" t="s">
+      <c r="Z67" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA67" s="21" t="s">
         <v>557</v>
       </c>
-      <c r="AB67" s="79" t="s">
+      <c r="AB67" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC67" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD67" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="69">
         <v>68</v>
       </c>
@@ -10870,20 +11058,23 @@
       <c r="Y68" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z68" s="79" t="s">
+      <c r="Z68" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA68" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB68" s="79" t="s">
+      <c r="AB68" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC68" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD68" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="69">
         <v>69</v>
       </c>
@@ -10967,20 +11158,23 @@
       <c r="Y69" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z69" s="79" t="s">
+      <c r="Z69" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA69" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB69" s="79" t="s">
+      <c r="AB69" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC69" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD69" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="69">
         <v>70</v>
       </c>
@@ -11064,20 +11258,23 @@
       <c r="Y70" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z70" s="79" t="s">
+      <c r="Z70" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA70" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB70" s="79" t="s">
+      <c r="AB70" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC70" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD70" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="69">
         <v>71</v>
       </c>
@@ -11161,20 +11358,23 @@
       <c r="Y71" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z71" s="79" t="s">
+      <c r="Z71" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA71" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB71" s="79" t="s">
+      <c r="AB71" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC71" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD71" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="69">
         <v>72</v>
       </c>
@@ -11258,20 +11458,23 @@
       <c r="Y72" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z72" s="79" t="s">
+      <c r="Z72" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA72" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB72" s="79" t="s">
+      <c r="AB72" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC72" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD72" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="69">
         <v>73</v>
       </c>
@@ -11355,20 +11558,23 @@
       <c r="Y73" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="Z73" s="79" t="s">
+      <c r="Z73" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA73" s="21" t="s">
         <v>558</v>
       </c>
-      <c r="AB73" s="79" t="s">
+      <c r="AB73" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC73" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD73" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="69">
         <v>74</v>
       </c>
@@ -11452,20 +11658,23 @@
       <c r="Y74" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z74" s="79" t="s">
+      <c r="Z74" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA74" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB74" s="79" t="s">
+      <c r="AB74" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC74" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD74" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="69">
         <v>75</v>
       </c>
@@ -11549,20 +11758,23 @@
       <c r="Y75" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z75" s="79" t="s">
+      <c r="Z75" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA75" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB75" s="79" t="s">
+      <c r="AB75" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC75" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD75" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="69">
         <v>76</v>
       </c>
@@ -11646,20 +11858,23 @@
       <c r="Y76" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z76" s="79" t="s">
+      <c r="Z76" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA76" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB76" s="79" t="s">
+      <c r="AB76" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC76" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD76" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="69">
         <v>77</v>
       </c>
@@ -11743,20 +11958,23 @@
       <c r="Y77" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z77" s="79" t="s">
+      <c r="Z77" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA77" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB77" s="79" t="s">
+      <c r="AB77" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC77" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD77" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="69">
         <v>78</v>
       </c>
@@ -11840,20 +12058,23 @@
       <c r="Y78" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z78" s="79" t="s">
+      <c r="Z78" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA78" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB78" s="79" t="s">
+      <c r="AB78" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC78" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD78" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="69">
         <v>79</v>
       </c>
@@ -11937,20 +12158,23 @@
       <c r="Y79" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z79" s="79" t="s">
+      <c r="Z79" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA79" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB79" s="79" t="s">
+      <c r="AB79" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC79" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD79" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="69">
         <v>80</v>
       </c>
@@ -12034,20 +12258,23 @@
       <c r="Y80" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z80" s="79" t="s">
+      <c r="Z80" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA80" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB80" s="79" t="s">
+      <c r="AB80" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC80" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD80" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="69">
         <v>81</v>
       </c>
@@ -12131,20 +12358,23 @@
       <c r="Y81" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z81" s="79" t="s">
+      <c r="Z81" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA81" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB81" s="79" t="s">
+      <c r="AB81" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC81" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD81" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="69">
         <v>82</v>
       </c>
@@ -12228,20 +12458,23 @@
       <c r="Y82" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z82" s="79" t="s">
+      <c r="Z82" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA82" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB82" s="79" t="s">
+      <c r="AB82" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC82" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD82" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="69">
         <v>83</v>
       </c>
@@ -12325,20 +12558,23 @@
       <c r="Y83" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z83" s="79" t="s">
+      <c r="Z83" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA83" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="AB83" s="79" t="s">
+      <c r="AB83" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC83" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD83" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="69">
         <v>84</v>
       </c>
@@ -12422,20 +12658,23 @@
       <c r="Y84" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z84" s="79" t="s">
+      <c r="Z84" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA84" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="AB84" s="79" t="s">
+      <c r="AB84" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC84" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD84" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="85" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="69">
         <v>85</v>
       </c>
@@ -12519,20 +12758,23 @@
       <c r="Y85" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z85" s="79" t="s">
+      <c r="Z85" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA85" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="AB85" s="79" t="s">
+      <c r="AB85" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC85" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD85" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="86" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="69">
         <v>86</v>
       </c>
@@ -12616,20 +12858,23 @@
       <c r="Y86" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z86" s="79" t="s">
+      <c r="Z86" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA86" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="AB86" s="79" t="s">
+      <c r="AB86" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC86" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD86" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="87" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="69">
         <v>87</v>
       </c>
@@ -12713,20 +12958,23 @@
       <c r="Y87" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z87" s="79" t="s">
+      <c r="Z87" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA87" s="21" t="s">
         <v>561</v>
       </c>
-      <c r="AB87" s="79" t="s">
+      <c r="AB87" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC87" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD87" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="69">
         <v>88</v>
       </c>
@@ -12810,20 +13058,23 @@
       <c r="Y88" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z88" s="79" t="s">
+      <c r="Z88" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA88" s="21" t="s">
         <v>561</v>
       </c>
-      <c r="AB88" s="79" t="s">
+      <c r="AB88" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC88" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD88" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="69">
         <v>89</v>
       </c>
@@ -12907,20 +13158,23 @@
       <c r="Y89" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z89" s="79" t="s">
+      <c r="Z89" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA89" s="21" t="s">
         <v>561</v>
       </c>
-      <c r="AB89" s="79" t="s">
+      <c r="AB89" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC89" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD89" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="69">
         <v>90</v>
       </c>
@@ -13004,20 +13258,23 @@
       <c r="Y90" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z90" s="79" t="s">
+      <c r="Z90" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA90" s="21" t="s">
         <v>562</v>
       </c>
-      <c r="AB90" s="79" t="s">
+      <c r="AB90" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC90" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD90" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="69">
         <v>91</v>
       </c>
@@ -13101,20 +13358,23 @@
       <c r="Y91" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z91" s="79" t="s">
+      <c r="Z91" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA91" s="68" t="s">
         <v>563</v>
       </c>
-      <c r="AB91" s="79" t="s">
+      <c r="AB91" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC91" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD91" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="69">
         <v>92</v>
       </c>
@@ -13198,20 +13458,23 @@
       <c r="Y92" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z92" s="79" t="s">
+      <c r="Z92" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA92" s="68" t="s">
         <v>564</v>
       </c>
-      <c r="AB92" s="79" t="s">
+      <c r="AB92" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC92" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD92" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="69">
         <v>93</v>
       </c>
@@ -13295,20 +13558,23 @@
       <c r="Y93" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z93" s="79" t="s">
+      <c r="Z93" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA93" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB93" s="79" t="s">
+      <c r="AB93" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC93" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD93" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="69">
         <v>94</v>
       </c>
@@ -13392,20 +13658,23 @@
       <c r="Y94" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z94" s="79" t="s">
+      <c r="Z94" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA94" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB94" s="79" t="s">
+      <c r="AB94" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC94" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD94" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="69">
         <v>95</v>
       </c>
@@ -13489,20 +13758,23 @@
       <c r="Y95" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z95" s="79" t="s">
+      <c r="Z95" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA95" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB95" s="79" t="s">
+      <c r="AB95" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC95" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD95" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="69">
         <v>96</v>
       </c>
@@ -13586,20 +13858,23 @@
       <c r="Y96" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z96" s="79" t="s">
+      <c r="Z96" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA96" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB96" s="79" t="s">
+      <c r="AB96" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC96" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD96" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="69">
         <v>97</v>
       </c>
@@ -13683,20 +13958,23 @@
       <c r="Y97" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z97" s="79" t="s">
+      <c r="Z97" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA97" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB97" s="79" t="s">
+      <c r="AB97" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC97" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD97" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="69">
         <v>98</v>
       </c>
@@ -13780,20 +14058,23 @@
       <c r="Y98" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z98" s="79" t="s">
+      <c r="Z98" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA98" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB98" s="79" t="s">
+      <c r="AB98" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC98" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD98" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="69">
         <v>99</v>
       </c>
@@ -13877,20 +14158,23 @@
       <c r="Y99" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z99" s="79" t="s">
+      <c r="Z99" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA99" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB99" s="79" t="s">
+      <c r="AB99" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC99" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD99" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="69">
         <v>100</v>
       </c>
@@ -13974,20 +14258,23 @@
       <c r="Y100" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z100" s="79" t="s">
+      <c r="Z100" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA100" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB100" s="79" t="s">
+      <c r="AB100" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC100" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD100" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="101" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="69">
         <v>101</v>
       </c>
@@ -14071,20 +14358,23 @@
       <c r="Y101" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z101" s="79" t="s">
+      <c r="Z101" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA101" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB101" s="79" t="s">
+      <c r="AB101" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC101" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD101" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="102" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="69">
         <v>102</v>
       </c>
@@ -14168,20 +14458,23 @@
       <c r="Y102" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z102" s="79" t="s">
+      <c r="Z102" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA102" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB102" s="79" t="s">
+      <c r="AB102" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC102" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD102" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="103" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="69">
         <v>103</v>
       </c>
@@ -14265,20 +14558,23 @@
       <c r="Y103" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z103" s="79" t="s">
+      <c r="Z103" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA103" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB103" s="79" t="s">
+      <c r="AB103" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC103" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD103" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="104" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="69">
         <v>104</v>
       </c>
@@ -14362,20 +14658,23 @@
       <c r="Y104" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z104" s="79" t="s">
+      <c r="Z104" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA104" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB104" s="79" t="s">
+      <c r="AB104" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC104" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD104" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="105" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="69">
         <v>105</v>
       </c>
@@ -14459,20 +14758,23 @@
       <c r="Y105" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z105" s="79" t="s">
+      <c r="Z105" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA105" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB105" s="79" t="s">
+      <c r="AB105" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC105" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD105" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="106" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="69">
         <v>106</v>
       </c>
@@ -14556,20 +14858,23 @@
       <c r="Y106" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z106" s="79" t="s">
+      <c r="Z106" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA106" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB106" s="79" t="s">
+      <c r="AB106" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC106" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD106" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="107" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="69">
         <v>107</v>
       </c>
@@ -14653,20 +14958,23 @@
       <c r="Y107" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z107" s="79" t="s">
+      <c r="Z107" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA107" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB107" s="79" t="s">
+      <c r="AB107" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC107" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD107" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="108" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="69">
         <v>108</v>
       </c>
@@ -14750,20 +15058,23 @@
       <c r="Y108" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z108" s="79" t="s">
+      <c r="Z108" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA108" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB108" s="79" t="s">
+      <c r="AB108" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC108" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD108" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="109" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="69">
         <v>109</v>
       </c>
@@ -14847,20 +15158,23 @@
       <c r="Y109" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z109" s="79" t="s">
+      <c r="Z109" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA109" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB109" s="79" t="s">
+      <c r="AB109" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC109" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD109" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="110" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="69">
         <v>110</v>
       </c>
@@ -14944,20 +15258,23 @@
       <c r="Y110" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z110" s="79" t="s">
+      <c r="Z110" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA110" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB110" s="79" t="s">
+      <c r="AB110" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC110" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD110" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="111" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="69">
         <v>111</v>
       </c>
@@ -15041,20 +15358,23 @@
       <c r="Y111" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z111" s="79" t="s">
+      <c r="Z111" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA111" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB111" s="79" t="s">
+      <c r="AB111" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC111" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD111" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="112" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="69">
         <v>112</v>
       </c>
@@ -15138,20 +15458,23 @@
       <c r="Y112" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z112" s="79" t="s">
+      <c r="Z112" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA112" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB112" s="79" t="s">
+      <c r="AB112" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC112" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD112" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="113" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="69">
         <v>113</v>
       </c>
@@ -15235,20 +15558,23 @@
       <c r="Y113" s="21" t="s">
         <v>554</v>
       </c>
-      <c r="Z113" s="79" t="s">
+      <c r="Z113" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA113" s="21" t="s">
         <v>565</v>
       </c>
-      <c r="AB113" s="79" t="s">
+      <c r="AB113" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC113" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD113" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="114" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="69">
         <v>114</v>
       </c>
@@ -15332,20 +15658,23 @@
       <c r="Y114" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z114" s="79" t="s">
+      <c r="Z114" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA114" s="21" t="s">
         <v>567</v>
       </c>
-      <c r="AB114" s="79" t="s">
+      <c r="AB114" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC114" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD114" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="115" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="69">
         <v>115</v>
       </c>
@@ -15429,20 +15758,23 @@
       <c r="Y115" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z115" s="79" t="s">
+      <c r="Z115" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA115" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB115" s="79" t="s">
+      <c r="AB115" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC115" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD115" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="116" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="69">
         <v>116</v>
       </c>
@@ -15526,20 +15858,23 @@
       <c r="Y116" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z116" s="79" t="s">
+      <c r="Z116" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA116" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB116" s="79" t="s">
+      <c r="AB116" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC116" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD116" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="117" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="69">
         <v>117</v>
       </c>
@@ -15620,20 +15955,23 @@
       <c r="Y117" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z117" s="79" t="s">
+      <c r="Z117" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA117" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB117" s="79" t="s">
+      <c r="AB117" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC117" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD117" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="118" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="69">
         <v>118</v>
       </c>
@@ -15714,20 +16052,23 @@
       <c r="Y118" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z118" s="79" t="s">
+      <c r="Z118" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA118" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB118" s="79" t="s">
+      <c r="AB118" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC118" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD118" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="119" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="69">
         <v>119</v>
       </c>
@@ -15808,20 +16149,23 @@
       <c r="Y119" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z119" s="79" t="s">
+      <c r="Z119" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA119" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB119" s="79" t="s">
+      <c r="AB119" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC119" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD119" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="120" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="69">
         <v>120</v>
       </c>
@@ -15902,20 +16246,23 @@
       <c r="Y120" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z120" s="79" t="s">
+      <c r="Z120" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA120" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB120" s="79" t="s">
+      <c r="AB120" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC120" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD120" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="121" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="69">
         <v>121</v>
       </c>
@@ -15996,20 +16343,23 @@
       <c r="Y121" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="Z121" s="79" t="s">
+      <c r="Z121" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA121" s="21" t="s">
         <v>568</v>
       </c>
-      <c r="AB121" s="79" t="s">
+      <c r="AB121" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC121" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD121" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="122" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="69">
         <v>122</v>
       </c>
@@ -16090,20 +16440,23 @@
       <c r="Y122" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z122" s="79" t="s">
+      <c r="Z122" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA122" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB122" s="79" t="s">
+      <c r="AB122" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC122" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD122" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="123" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="69">
         <v>123</v>
       </c>
@@ -16184,20 +16537,23 @@
       <c r="Y123" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z123" s="79" t="s">
+      <c r="Z123" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA123" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB123" s="79" t="s">
+      <c r="AB123" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC123" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD123" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="124" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="69">
         <v>124</v>
       </c>
@@ -16278,20 +16634,23 @@
       <c r="Y124" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z124" s="79" t="s">
+      <c r="Z124" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA124" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB124" s="79" t="s">
+      <c r="AB124" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC124" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD124" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="125" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="69">
         <v>125</v>
       </c>
@@ -16372,20 +16731,23 @@
       <c r="Y125" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z125" s="79" t="s">
+      <c r="Z125" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA125" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB125" s="79" t="s">
+      <c r="AB125" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC125" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD125" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="126" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="69">
         <v>126</v>
       </c>
@@ -16460,26 +16822,29 @@
         <v>521</v>
       </c>
       <c r="X126" s="71" t="str">
-        <f t="shared" ref="X126:X129" si="26">CONCATENATE("Key-TUB-",A126)</f>
+        <f t="shared" ref="X126:X133" si="26">CONCATENATE("Key-TUB-",A126)</f>
         <v>Key-TUB-126</v>
       </c>
       <c r="Y126" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z126" s="79" t="s">
+      <c r="Z126" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA126" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB126" s="79" t="s">
+      <c r="AB126" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC126" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD126" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="127" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="69">
         <v>127</v>
       </c>
@@ -16560,20 +16925,23 @@
       <c r="Y127" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z127" s="79" t="s">
+      <c r="Z127" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA127" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB127" s="79" t="s">
+      <c r="AB127" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC127" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD127" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="128" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="69">
         <v>128</v>
       </c>
@@ -16608,7 +16976,7 @@
         <v>9</v>
       </c>
       <c r="L128" s="25" t="str">
-        <f t="shared" ref="L128:O129" si="27">SUBSTITUTE(CONCATENATE("", C128), ".", " ")</f>
+        <f t="shared" ref="L128:O133" si="27">SUBSTITUTE(CONCATENATE("", C128), ".", " ")</f>
         <v>De Tubulações</v>
       </c>
       <c r="M128" s="25" t="str">
@@ -16654,36 +17022,39 @@
       <c r="Y128" s="21" t="s">
         <v>841</v>
       </c>
-      <c r="Z128" s="79" t="s">
+      <c r="Z128" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AA128" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="AB128" s="79" t="s">
+      <c r="AB128" s="78" t="s">
         <v>9</v>
       </c>
       <c r="AC128" s="21" t="s">
         <v>526</v>
       </c>
+      <c r="AD128" s="78" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="129" spans="1:29" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:30" s="79" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="69">
         <v>129</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="C129" s="81" t="s">
+      <c r="C129" s="80" t="s">
         <v>870</v>
       </c>
-      <c r="D129" s="81" t="s">
+      <c r="D129" s="80" t="s">
         <v>872</v>
       </c>
-      <c r="E129" s="81" t="s">
+      <c r="E129" s="80" t="s">
         <v>871</v>
       </c>
-      <c r="F129" s="81" t="s">
+      <c r="F129" s="80" t="s">
         <v>873</v>
       </c>
       <c r="G129" s="70" t="s">
@@ -16715,32 +17086,30 @@
       </c>
       <c r="O129" s="25" t="str">
         <f t="shared" si="27"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P129" s="21" t="s">
         <v>874</v>
       </c>
-      <c r="Q129" s="77" t="str">
-        <f t="shared" ref="Q129" si="31">_xlfn.TRANSLATE(P129,"pt","es")</f>
-        <v>Aplicación Revit</v>
-      </c>
-      <c r="R129" s="77" t="str">
-        <f t="shared" ref="R129" si="32">_xlfn.TRANSLATE(P129,"pt","en")</f>
-        <v>Revit App</v>
+      <c r="Q129" s="21" t="s">
+        <v>875</v>
+      </c>
+      <c r="R129" s="21" t="s">
+        <v>876</v>
       </c>
       <c r="S129" s="21" t="s">
         <v>9</v>
       </c>
       <c r="T129" s="21" t="str">
-        <f t="shared" ref="T129:V129" si="33">SUBSTITUTE(C129, ".", " ")</f>
+        <f t="shared" ref="T129:V133" si="31">SUBSTITUTE(C129, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U129" s="21" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>Macros</v>
       </c>
-      <c r="V129" s="78" t="str">
-        <f t="shared" si="33"/>
+      <c r="V129" s="77" t="str">
+        <f t="shared" si="31"/>
         <v>Métodos</v>
       </c>
       <c r="W129" s="21" t="s">
@@ -16750,60 +17119,454 @@
         <f t="shared" si="26"/>
         <v>Key-TUB-129</v>
       </c>
-      <c r="Y129" s="79" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z129" s="79" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA129" s="79" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB129" s="79" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC129" s="79" t="s">
+      <c r="Y129" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z129" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA129" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB129" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC129" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD129" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:30" s="79" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="69">
+        <v>130</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="C130" s="80" t="s">
+        <v>870</v>
+      </c>
+      <c r="D130" s="80" t="s">
+        <v>872</v>
+      </c>
+      <c r="E130" s="80" t="s">
+        <v>871</v>
+      </c>
+      <c r="F130" s="80" t="s">
+        <v>877</v>
+      </c>
+      <c r="G130" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H130" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I130" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J130" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="K130" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="L130" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>De API</v>
+      </c>
+      <c r="M130" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Macros</v>
+      </c>
+      <c r="N130" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O130" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P130" s="21" t="s">
+        <v>878</v>
+      </c>
+      <c r="Q130" s="21" t="s">
+        <v>879</v>
+      </c>
+      <c r="R130" s="21" t="s">
+        <v>880</v>
+      </c>
+      <c r="S130" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T130" s="21" t="str">
+        <f t="shared" si="31"/>
+        <v>De API</v>
+      </c>
+      <c r="U130" s="21" t="str">
+        <f t="shared" si="31"/>
+        <v>Macros</v>
+      </c>
+      <c r="V130" s="77" t="str">
+        <f t="shared" si="31"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W130" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="X130" s="71" t="str">
+        <f t="shared" si="26"/>
+        <v>Key-TUB-130</v>
+      </c>
+      <c r="Y130" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z130" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA130" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB130" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC130" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD130" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:30" s="79" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="69">
+        <v>131</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="C131" s="80" t="s">
+        <v>870</v>
+      </c>
+      <c r="D131" s="80" t="s">
+        <v>872</v>
+      </c>
+      <c r="E131" s="80" t="s">
+        <v>871</v>
+      </c>
+      <c r="F131" s="80" t="s">
+        <v>881</v>
+      </c>
+      <c r="G131" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H131" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I131" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J131" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="K131" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="L131" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>De API</v>
+      </c>
+      <c r="M131" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Macros</v>
+      </c>
+      <c r="N131" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O131" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P131" s="21" t="s">
+        <v>882</v>
+      </c>
+      <c r="Q131" s="21" t="s">
+        <v>883</v>
+      </c>
+      <c r="R131" s="21" t="s">
+        <v>884</v>
+      </c>
+      <c r="S131" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T131" s="21" t="str">
+        <f t="shared" si="31"/>
+        <v>De API</v>
+      </c>
+      <c r="U131" s="21" t="str">
+        <f t="shared" si="31"/>
+        <v>Macros</v>
+      </c>
+      <c r="V131" s="77" t="str">
+        <f t="shared" si="31"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W131" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="X131" s="71" t="str">
+        <f t="shared" si="26"/>
+        <v>Key-TUB-131</v>
+      </c>
+      <c r="Y131" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z131" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA131" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB131" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC131" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD131" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:30" s="79" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="69">
+        <v>132</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="C132" s="80" t="s">
+        <v>870</v>
+      </c>
+      <c r="D132" s="80" t="s">
+        <v>872</v>
+      </c>
+      <c r="E132" s="80" t="s">
+        <v>871</v>
+      </c>
+      <c r="F132" s="80" t="s">
+        <v>885</v>
+      </c>
+      <c r="G132" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H132" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I132" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J132" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="K132" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="L132" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>De API</v>
+      </c>
+      <c r="M132" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Macros</v>
+      </c>
+      <c r="N132" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O132" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P132" s="21" t="s">
+        <v>886</v>
+      </c>
+      <c r="Q132" s="21" t="s">
+        <v>887</v>
+      </c>
+      <c r="R132" s="21" t="s">
+        <v>888</v>
+      </c>
+      <c r="S132" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T132" s="21" t="str">
+        <f t="shared" si="31"/>
+        <v>De API</v>
+      </c>
+      <c r="U132" s="21" t="str">
+        <f t="shared" si="31"/>
+        <v>Macros</v>
+      </c>
+      <c r="V132" s="77" t="str">
+        <f t="shared" si="31"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W132" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="X132" s="71" t="str">
+        <f t="shared" si="26"/>
+        <v>Key-TUB-132</v>
+      </c>
+      <c r="Y132" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z132" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA132" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB132" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC132" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD132" s="78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:30" s="79" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="69">
+        <v>133</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="C133" s="80" t="s">
+        <v>870</v>
+      </c>
+      <c r="D133" s="80" t="s">
+        <v>872</v>
+      </c>
+      <c r="E133" s="80" t="s">
+        <v>889</v>
+      </c>
+      <c r="F133" s="80" t="s">
+        <v>890</v>
+      </c>
+      <c r="G133" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H133" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I133" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J133" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="K133" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="L133" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>De API</v>
+      </c>
+      <c r="M133" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Macros</v>
+      </c>
+      <c r="N133" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O133" s="25" t="str">
+        <f t="shared" si="27"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P133" s="21" t="s">
+        <v>891</v>
+      </c>
+      <c r="Q133" s="21" t="s">
+        <v>892</v>
+      </c>
+      <c r="R133" s="21" t="s">
+        <v>893</v>
+      </c>
+      <c r="S133" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="T133" s="21" t="str">
+        <f t="shared" si="31"/>
+        <v>De API</v>
+      </c>
+      <c r="U133" s="21" t="str">
+        <f t="shared" si="31"/>
+        <v>Macros</v>
+      </c>
+      <c r="V133" s="77" t="str">
+        <f t="shared" si="31"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W133" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="X133" s="71" t="str">
+        <f t="shared" si="26"/>
+        <v>Key-TUB-133</v>
+      </c>
+      <c r="Y133" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z133" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA133" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB133" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC133" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD133" s="78" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B129">
-    <cfRule type="cellIs" dxfId="25" priority="5" operator="equal">
+  <conditionalFormatting sqref="A2:B133">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F121 F130:F1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="48"/>
+  <conditionalFormatting sqref="E133:F133">
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F121 F134:F1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F121">
-    <cfRule type="duplicateValues" dxfId="23" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F128 F130:F1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
+  <conditionalFormatting sqref="F1:F128 F134:F1048576">
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F129">
-    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q129">
-    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+  <conditionalFormatting sqref="F129:F132">
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R121">
-    <cfRule type="cellIs" dxfId="15" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R129">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y128 AA2:AA128 AC2:AC128">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16815,15 +17578,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -16888,7 +17651,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -16953,7 +17716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -17036,55 +17799,55 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:AQ61"/>
-  <sheetFormatPr defaultColWidth="5.3046875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="5.28515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3046875" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.69140625" style="34" customWidth="1"/>
-    <col min="3" max="3" width="9.3046875" style="45" customWidth="1"/>
-    <col min="4" max="4" width="7.69140625" style="34" customWidth="1"/>
-    <col min="5" max="5" width="11.69140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.3046875" style="45" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.3828125" style="45" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.3828125" style="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="34" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="45" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="34" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.28515625" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.42578125" style="45" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="45" customWidth="1"/>
-    <col min="10" max="10" width="3.15234375" style="45" customWidth="1"/>
-    <col min="11" max="11" width="3.69140625" style="45" customWidth="1"/>
-    <col min="12" max="12" width="3.69140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.3046875" style="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.69140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.84375" style="34" customWidth="1"/>
-    <col min="16" max="16" width="7.84375" style="45" customWidth="1"/>
-    <col min="17" max="17" width="3.3046875" style="44" customWidth="1"/>
-    <col min="18" max="18" width="7.84375" style="34" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.53515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.140625" style="45" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" style="45" customWidth="1"/>
+    <col min="12" max="12" width="3.7109375" style="45" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.28515625" style="45" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" style="45" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" style="34" customWidth="1"/>
+    <col min="16" max="16" width="7.85546875" style="45" customWidth="1"/>
+    <col min="17" max="17" width="3.28515625" style="44" customWidth="1"/>
+    <col min="18" max="18" width="7.85546875" style="34" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.5703125" style="44" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13" style="34" customWidth="1"/>
-    <col min="21" max="21" width="3.3046875" style="44" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.3046875" style="34" customWidth="1"/>
-    <col min="23" max="23" width="4.15234375" style="34" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.15234375" style="45" customWidth="1"/>
-    <col min="25" max="25" width="3.69140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.69140625" style="45" customWidth="1"/>
-    <col min="27" max="27" width="3.3046875" style="34" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.28515625" style="44" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" style="34" customWidth="1"/>
+    <col min="23" max="23" width="4.140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.140625" style="45" customWidth="1"/>
+    <col min="25" max="25" width="3.7109375" style="34" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" style="45" customWidth="1"/>
+    <col min="27" max="27" width="3.28515625" style="34" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9" style="34" customWidth="1"/>
     <col min="29" max="29" width="4" style="44" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="6" style="34" customWidth="1"/>
-    <col min="31" max="31" width="4.53515625" style="44" customWidth="1"/>
-    <col min="32" max="32" width="7.84375" style="34" customWidth="1"/>
-    <col min="33" max="33" width="12.84375" style="34" customWidth="1"/>
-    <col min="34" max="34" width="4.69140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.3046875" style="34" customWidth="1"/>
-    <col min="36" max="36" width="5.3046875" style="45"/>
-    <col min="37" max="37" width="46.69140625" style="34" customWidth="1"/>
+    <col min="31" max="31" width="4.5703125" style="44" customWidth="1"/>
+    <col min="32" max="32" width="7.85546875" style="34" customWidth="1"/>
+    <col min="33" max="33" width="12.85546875" style="34" customWidth="1"/>
+    <col min="34" max="34" width="4.7109375" style="45" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="34" customWidth="1"/>
+    <col min="36" max="36" width="5.28515625" style="45"/>
+    <col min="37" max="37" width="46.7109375" style="34" customWidth="1"/>
     <col min="38" max="38" width="7" style="34" customWidth="1"/>
     <col min="39" max="39" width="12" style="34" customWidth="1"/>
-    <col min="40" max="40" width="5.3046875" style="34"/>
+    <col min="40" max="40" width="5.28515625" style="34"/>
     <col min="41" max="41" width="10" style="34" customWidth="1"/>
-    <col min="42" max="42" width="6.15234375" style="34" customWidth="1"/>
-    <col min="43" max="43" width="11.3046875" style="34" customWidth="1"/>
-    <col min="44" max="16384" width="5.3046875" style="34"/>
+    <col min="42" max="42" width="6.140625" style="34" customWidth="1"/>
+    <col min="43" max="43" width="11.28515625" style="34" customWidth="1"/>
+    <col min="44" max="16384" width="5.28515625" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
@@ -17211,7 +17974,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -17342,7 +18105,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -17473,7 +18236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -17604,7 +18367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -17736,7 +18499,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -17868,7 +18631,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -18000,7 +18763,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -18132,7 +18895,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -18264,7 +19027,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -18396,7 +19159,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -18528,7 +19291,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -18660,7 +19423,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -18792,7 +19555,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="14" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -18924,7 +19687,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="15" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -19056,7 +19819,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -19188,7 +19951,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="17" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -19320,7 +20083,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="18" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -19452,7 +20215,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="19" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -19584,7 +20347,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -19716,7 +20479,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -19848,7 +20611,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="22" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -19980,7 +20743,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="23" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -20112,7 +20875,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="24" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -20244,7 +21007,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="25" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -20376,7 +21139,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="26" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -20508,7 +21271,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="27" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -20640,7 +21403,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="28" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -20772,7 +21535,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="29" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -20904,7 +21667,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="30" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -21036,7 +21799,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="31" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -21168,7 +21931,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="32" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -21300,7 +22063,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="33" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -21432,7 +22195,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="34" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -21564,7 +22327,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="35" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -21696,7 +22459,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="36" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -21828,7 +22591,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="37" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -21960,7 +22723,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>38</v>
       </c>
@@ -22092,7 +22855,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="39" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>39</v>
       </c>
@@ -22224,7 +22987,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="40" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>40</v>
       </c>
@@ -22356,7 +23119,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="41" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>41</v>
       </c>
@@ -22488,7 +23251,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="42" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>42</v>
       </c>
@@ -22620,7 +23383,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="43" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <v>43</v>
       </c>
@@ -22752,7 +23515,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="44" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <v>44</v>
       </c>
@@ -22884,7 +23647,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="45" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <v>45</v>
       </c>
@@ -23016,7 +23779,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="46" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16">
         <v>46</v>
       </c>
@@ -23148,7 +23911,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="47" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16">
         <v>47</v>
       </c>
@@ -23280,7 +24043,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="48" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
         <v>48</v>
       </c>
@@ -23412,7 +24175,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="49" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16">
         <v>49</v>
       </c>
@@ -23544,7 +24307,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="50" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16">
         <v>50</v>
       </c>
@@ -23676,7 +24439,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="51" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16">
         <v>51</v>
       </c>
@@ -23808,7 +24571,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="52" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16">
         <v>52</v>
       </c>
@@ -23940,7 +24703,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="53" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <v>53</v>
       </c>
@@ -24072,7 +24835,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="54" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
         <v>54</v>
       </c>
@@ -24204,7 +24967,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="55" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
         <v>55</v>
       </c>
@@ -24336,7 +25099,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="56" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <v>56</v>
       </c>
@@ -24468,7 +25231,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="57" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
         <v>57</v>
       </c>
@@ -24600,7 +25363,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="58" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16">
         <v>58</v>
       </c>
@@ -24731,7 +25494,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="59" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
         <v>59</v>
       </c>
@@ -24862,7 +25625,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="60" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
         <v>60</v>
       </c>
@@ -24993,7 +25756,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="61" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:43" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
         <v>61</v>
       </c>
@@ -25157,15 +25920,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" style="18" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22">
         <v>0</v>
       </c>
@@ -25188,7 +25951,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -25211,7 +25974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>3</v>
       </c>
@@ -25234,7 +25997,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>4</v>
       </c>
@@ -25257,7 +26020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>5</v>
       </c>
@@ -25280,7 +26043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
         <v>6</v>
       </c>
@@ -25303,7 +26066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
         <v>7</v>
       </c>
@@ -25326,7 +26089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
         <v>8</v>
       </c>
@@ -25349,7 +26112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
         <v>9</v>
       </c>
@@ -25372,7 +26135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
         <v>10</v>
       </c>
@@ -25395,7 +26158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
         <v>11</v>
       </c>
@@ -25418,7 +26181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
         <v>12</v>
       </c>
@@ -25441,7 +26204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
         <v>13</v>
       </c>
@@ -25464,7 +26227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
         <v>14</v>
       </c>
@@ -25487,7 +26250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
         <v>15</v>
       </c>
